--- a/Campaigns_Master.xlsx
+++ b/Campaigns_Master.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Good KoDz\Banner Monitor\Version_0.2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Good KoDz\Banner Monitor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3B84753-C2CC-462C-BD31-C3985E8A1059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0483A63F-1C18-47B9-95A4-B820A828B9BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EBB7D5F9-BF11-4273-8F7B-7CCC7D024DDF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1316" uniqueCount="983">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1326" uniqueCount="984">
   <si>
     <t>Campaign Name</t>
   </si>
@@ -2985,6 +2985,9 @@
   </si>
   <si>
     <t>https://adserver.doctoreto.com/www/images/1f0974b8fa9ab88359f29073de03f5ff.gif</t>
+  </si>
+  <si>
+    <t>Nastaran</t>
   </si>
 </sst>
 </file>
@@ -2995,7 +2998,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3006,6 +3009,12 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -3930,225 +3939,233 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>46</v>
+        <v>52</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>53</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="H8" s="12">
-        <v>190000000</v>
+        <v>143000000</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>61</v>
       </c>
       <c r="H9" s="12">
-        <v>143000000</v>
+        <v>80000000</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="G10" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="G10" s="1" t="s">
         <v>61</v>
       </c>
       <c r="H10" s="12">
-        <v>80000000</v>
+        <v>168000000</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>71</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="H11" s="12">
-        <v>168000000</v>
+        <v>66000000</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F12" s="10" t="s">
-        <v>71</v>
+        <v>76</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>77</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="H12" s="12">
-        <v>66000000</v>
+        <v>40100000</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
+      </c>
+      <c r="F13" s="13" t="s">
+        <v>83</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="H13" s="12">
-        <v>40100000</v>
+        <v>44000000</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="F14" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="G14" s="1"/>
-      <c r="H14" s="12"/>
+        <v>88</v>
+      </c>
+      <c r="F14" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H14" s="12">
+        <v>70000000</v>
+      </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="F15" s="14" t="s">
-        <v>89</v>
+        <v>93</v>
+      </c>
+      <c r="F15" s="15" t="s">
+        <v>94</v>
       </c>
       <c r="G15" s="1"/>
       <c r="H15" s="12"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>91</v>
+        <v>43</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>92</v>
+        <v>44</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="F16" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="G16" s="1"/>
-      <c r="H16" s="12"/>
+        <v>95</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H16" s="12">
+        <v>190000000</v>
+      </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
@@ -4169,8 +4186,12 @@
       <c r="F17" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="G17" s="1"/>
-      <c r="H17" s="12"/>
+      <c r="G17" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H17" s="12">
+        <v>190000000</v>
+      </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
@@ -4191,8 +4212,12 @@
       <c r="F18" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="G18" s="1"/>
-      <c r="H18" s="12"/>
+      <c r="G18" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H18" s="12">
+        <v>190000000</v>
+      </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
@@ -4213,7 +4238,9 @@
       <c r="F19" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="G19" s="1"/>
+      <c r="G19" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="H19" s="12"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
@@ -4235,7 +4262,9 @@
       <c r="F20" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="G20" s="1"/>
+      <c r="G20" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="H20" s="12"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
@@ -4257,8 +4286,12 @@
       <c r="F21" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="G21" s="1"/>
-      <c r="H21" s="12"/>
+      <c r="G21" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H21" s="12">
+        <v>78000000</v>
+      </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
@@ -4279,8 +4312,12 @@
       <c r="F22" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="G22" s="1"/>
-      <c r="H22" s="12"/>
+      <c r="G22" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H22" s="12">
+        <v>66000000</v>
+      </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
@@ -4323,8 +4360,12 @@
       <c r="F24" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="G24" s="1"/>
-      <c r="H24" s="12"/>
+      <c r="G24" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H24" s="12">
+        <v>50000000</v>
+      </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
@@ -4345,8 +4386,12 @@
       <c r="F25" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="G25" s="1"/>
-      <c r="H25" s="12"/>
+      <c r="G25" s="1" t="s">
+        <v>983</v>
+      </c>
+      <c r="H25" s="12">
+        <v>45000000</v>
+      </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
@@ -8612,6 +8657,7 @@
       <c r="F230"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Campaigns_Master.xlsx
+++ b/Campaigns_Master.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Good KoDz\Banner Monitor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0483A63F-1C18-47B9-95A4-B820A828B9BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4CE86CC-04F4-4110-A083-6F72CFC43DB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EBB7D5F9-BF11-4273-8F7B-7CCC7D024DDF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId2"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1326" uniqueCount="984">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1343" uniqueCount="984">
   <si>
     <t>Campaign Name</t>
   </si>
@@ -3322,7 +3325,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -3345,12 +3348,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -3406,6 +3420,7 @@
     <xf numFmtId="0" fontId="0" fillId="49" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="50" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -3422,6 +3437,798 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Sheet1"/>
+      <sheetName val="Sheet2"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="A1" t="str">
+            <v>Campaign Name</v>
+          </cell>
+          <cell r="B1" t="str">
+            <v>Account Manager</v>
+          </cell>
+          <cell r="C1" t="str">
+            <v>Start Date</v>
+          </cell>
+          <cell r="D1" t="str">
+            <v>End Date</v>
+          </cell>
+          <cell r="E1" t="str">
+            <v>Price</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="A2" t="str">
+            <v>Dr Amir Azizi</v>
+          </cell>
+          <cell r="B2" t="str">
+            <v>Sanam</v>
+          </cell>
+          <cell r="C2" t="str">
+            <v>1405/04/06</v>
+          </cell>
+          <cell r="D2" t="str">
+            <v>1405/07/06</v>
+          </cell>
+          <cell r="E2">
+            <v>30600000</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="A3" t="str">
+            <v>DR Ali Saeedi</v>
+          </cell>
+          <cell r="B3" t="str">
+            <v>shahrzad</v>
+          </cell>
+          <cell r="C3" t="str">
+            <v>1405/03/26</v>
+          </cell>
+          <cell r="D3" t="str">
+            <v>1405/06/25</v>
+          </cell>
+          <cell r="E3">
+            <v>55000000</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="A4" t="str">
+            <v>DR Ali NaserBakhT</v>
+          </cell>
+          <cell r="B4" t="str">
+            <v>elahe</v>
+          </cell>
+          <cell r="C4" t="str">
+            <v>1405/02/29</v>
+          </cell>
+          <cell r="D4" t="str">
+            <v>1405/05/29</v>
+          </cell>
+          <cell r="E4">
+            <v>132000000</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="A5" t="str">
+            <v>Dr AssaEi</v>
+          </cell>
+          <cell r="B5" t="str">
+            <v>Nastaran</v>
+          </cell>
+          <cell r="C5" t="str">
+            <v>1405/05/26</v>
+          </cell>
+          <cell r="D5" t="str">
+            <v>1405/08/26</v>
+          </cell>
+          <cell r="E5">
+            <v>20000000</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="A6" t="str">
+            <v>DR Azadeh Khalajian</v>
+          </cell>
+          <cell r="B6" t="str">
+            <v>Sanam</v>
+          </cell>
+          <cell r="C6" t="str">
+            <v>1405/03/15</v>
+          </cell>
+          <cell r="D6" t="str">
+            <v>1405/06/15</v>
+          </cell>
+          <cell r="E6">
+            <v>60000000</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7" t="str">
+            <v>Dr Atefe Faramarzi</v>
+          </cell>
+          <cell r="B7" t="str">
+            <v>Naser</v>
+          </cell>
+          <cell r="C7" t="str">
+            <v>1405/05/05</v>
+          </cell>
+          <cell r="D7" t="str">
+            <v>1405/08/05</v>
+          </cell>
+          <cell r="E7">
+            <v>135000000</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="A8" t="str">
+            <v>DR Ata Heydari</v>
+          </cell>
+          <cell r="B8" t="str">
+            <v>Naser</v>
+          </cell>
+          <cell r="E8">
+            <v>150000000</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="A9" t="str">
+            <v>Dr Azhie</v>
+          </cell>
+          <cell r="B9" t="str">
+            <v>Naser</v>
+          </cell>
+          <cell r="C9" t="str">
+            <v>1405/05/19</v>
+          </cell>
+          <cell r="D9" t="str">
+            <v>1405/08/19</v>
+          </cell>
+          <cell r="E9">
+            <v>140000000</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="A10" t="str">
+            <v>Dr Azadeh MirMaasoumi</v>
+          </cell>
+          <cell r="B10" t="str">
+            <v>Sara</v>
+          </cell>
+          <cell r="C10" t="str">
+            <v>1405/03/16</v>
+          </cell>
+          <cell r="D10" t="str">
+            <v>1405/05/16</v>
+          </cell>
+          <cell r="E10">
+            <v>45000000</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="A11" t="str">
+            <v>Dr Homa Sharifi</v>
+          </cell>
+          <cell r="B11" t="str">
+            <v>Sara</v>
+          </cell>
+          <cell r="C11" t="str">
+            <v>1405/04/08</v>
+          </cell>
+          <cell r="D11" t="str">
+            <v>1405/07/08</v>
+          </cell>
+          <cell r="E11">
+            <v>27000000</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="A12" t="str">
+            <v>Dr Zarin BadiNi</v>
+          </cell>
+          <cell r="B12" t="str">
+            <v>Sanam</v>
+          </cell>
+          <cell r="C12" t="str">
+            <v>1405/04/29</v>
+          </cell>
+          <cell r="D12" t="str">
+            <v>1405/07/29</v>
+          </cell>
+          <cell r="E12">
+            <v>240000000</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="A13" t="str">
+            <v>DR Zeynab Tavana</v>
+          </cell>
+          <cell r="B13" t="str">
+            <v>Nastaran</v>
+          </cell>
+          <cell r="C13" t="str">
+            <v>1405/05/19</v>
+          </cell>
+          <cell r="D13" t="str">
+            <v>1405/08/19</v>
+          </cell>
+          <cell r="E13">
+            <v>8800000</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="A14" t="str">
+            <v>Dr. Farshad Sadeghi</v>
+          </cell>
+          <cell r="B14" t="str">
+            <v>Sara</v>
+          </cell>
+          <cell r="C14" t="str">
+            <v>1405/04/10</v>
+          </cell>
+          <cell r="D14" t="str">
+            <v>1405/07/10</v>
+          </cell>
+          <cell r="E14">
+            <v>60000000</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="A15" t="str">
+            <v>Dr. Amir Bastani</v>
+          </cell>
+          <cell r="B15" t="str">
+            <v>Nastaran</v>
+          </cell>
+          <cell r="C15" t="str">
+            <v>1405/03/09</v>
+          </cell>
+          <cell r="D15" t="str">
+            <v>1405/06/09</v>
+          </cell>
+          <cell r="E15">
+            <v>36000000</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="A16" t="str">
+            <v>Dr. Ghazi</v>
+          </cell>
+          <cell r="B16" t="str">
+            <v>Naser</v>
+          </cell>
+          <cell r="C16" t="str">
+            <v>1405/06/04</v>
+          </cell>
+          <cell r="D16" t="str">
+            <v>1405/09/04</v>
+          </cell>
+          <cell r="E16">
+            <v>427000000</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="A17" t="str">
+            <v>Dr. Hadi Mansouri</v>
+          </cell>
+          <cell r="B17" t="str">
+            <v>Nastaran</v>
+          </cell>
+          <cell r="C17" t="str">
+            <v>1405/04/02</v>
+          </cell>
+          <cell r="D17" t="str">
+            <v>1405/07/02</v>
+          </cell>
+          <cell r="E17">
+            <v>46200000</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="A18" t="str">
+            <v>Dr. Izadpanah</v>
+          </cell>
+          <cell r="B18" t="str">
+            <v>Sara</v>
+          </cell>
+          <cell r="C18" t="str">
+            <v>1405/04/28</v>
+          </cell>
+          <cell r="D18" t="str">
+            <v>1405/07/28</v>
+          </cell>
+          <cell r="E18">
+            <v>75000000</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="A19" t="str">
+            <v>Dr. Hengame Mehrfar</v>
+          </cell>
+          <cell r="B19" t="str">
+            <v>shahrzad</v>
+          </cell>
+          <cell r="C19" t="str">
+            <v>1405/05/25</v>
+          </cell>
+          <cell r="D19" t="str">
+            <v>1405/08/25</v>
+          </cell>
+          <cell r="E19">
+            <v>46200000</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="A20" t="str">
+            <v>Dr. Mohammad Borzoyi</v>
+          </cell>
+          <cell r="B20" t="str">
+            <v>shahrzad</v>
+          </cell>
+          <cell r="C20" t="str">
+            <v>1405/03/04</v>
+          </cell>
+          <cell r="D20" t="str">
+            <v>1405/06/04</v>
+          </cell>
+          <cell r="E20">
+            <v>49500000</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="A21" t="str">
+            <v>Dr. Mayryam Farokhshahi</v>
+          </cell>
+          <cell r="B21" t="str">
+            <v>shahrzad</v>
+          </cell>
+          <cell r="C21" t="str">
+            <v>1405/06/02</v>
+          </cell>
+          <cell r="D21" t="str">
+            <v>1405/09/02</v>
+          </cell>
+          <cell r="E21">
+            <v>6600000</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="A22" t="str">
+            <v>Dr. Kartalayi</v>
+          </cell>
+          <cell r="B22" t="str">
+            <v>shahrzad</v>
+          </cell>
+          <cell r="C22" t="str">
+            <v>1405/05/29</v>
+          </cell>
+          <cell r="D22" t="str">
+            <v>1405/08/29</v>
+          </cell>
+          <cell r="E22">
+            <v>41580000</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="A23" t="str">
+            <v>Dr. Negin Asna Asahari</v>
+          </cell>
+          <cell r="B23" t="str">
+            <v>Nastaran</v>
+          </cell>
+          <cell r="C23" t="str">
+            <v>1405/06/16</v>
+          </cell>
+          <cell r="D23" t="str">
+            <v>1405/09/16</v>
+          </cell>
+          <cell r="E23">
+            <v>23100000</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="A24" t="str">
+            <v>Dr. Natami</v>
+          </cell>
+          <cell r="B24" t="str">
+            <v>Nastaran</v>
+          </cell>
+          <cell r="C24" t="str">
+            <v>1405/03/25</v>
+          </cell>
+          <cell r="D24" t="str">
+            <v>1405/06/25</v>
+          </cell>
+          <cell r="E24">
+            <v>33000000</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="A25" t="str">
+            <v>Dr. YazdanShenas</v>
+          </cell>
+          <cell r="B25" t="str">
+            <v>Nastaran</v>
+          </cell>
+          <cell r="C25" t="str">
+            <v>1405/03/17</v>
+          </cell>
+          <cell r="D25" t="str">
+            <v>1405/06/17</v>
+          </cell>
+          <cell r="E25">
+            <v>170000000</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="A26" t="str">
+            <v>Dr. Sahar Tavakoli</v>
+          </cell>
+          <cell r="B26" t="str">
+            <v>shahrzad</v>
+          </cell>
+          <cell r="C26" t="str">
+            <v>1405/06/16</v>
+          </cell>
+          <cell r="D26" t="str">
+            <v>1405/09/16</v>
+          </cell>
+          <cell r="E26">
+            <v>30000000</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="A27" t="str">
+            <v>Farzin Khorvash</v>
+          </cell>
+          <cell r="B27" t="str">
+            <v>Nastaran</v>
+          </cell>
+          <cell r="C27" t="str">
+            <v>1405/04/04</v>
+          </cell>
+          <cell r="D27" t="str">
+            <v>1405/07/04</v>
+          </cell>
+          <cell r="E27">
+            <v>49500000</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="A28" t="str">
+            <v>Farzane Mortazavi Far</v>
+          </cell>
+          <cell r="B28" t="str">
+            <v>Nastaran</v>
+          </cell>
+          <cell r="C28" t="str">
+            <v>1405/04/27</v>
+          </cell>
+          <cell r="D28" t="str">
+            <v>1405/07/27</v>
+          </cell>
+          <cell r="E28">
+            <v>72600000</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="A29" t="str">
+            <v>Farnaz Bagherian</v>
+          </cell>
+          <cell r="B29" t="str">
+            <v>Nastaran</v>
+          </cell>
+          <cell r="C29" t="str">
+            <v>1405/05/24</v>
+          </cell>
+          <cell r="D29" t="str">
+            <v>1405/08/24</v>
+          </cell>
+          <cell r="E29">
+            <v>6600000</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="A30" t="str">
+            <v>Hamed Mahmoudi</v>
+          </cell>
+          <cell r="B30" t="str">
+            <v>Naser</v>
+          </cell>
+          <cell r="C30" t="str">
+            <v>1405/05/06</v>
+          </cell>
+          <cell r="D30" t="str">
+            <v>1405/08/06</v>
+          </cell>
+          <cell r="E30">
+            <v>206000000</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="A31" t="str">
+            <v>Fateme Golestani</v>
+          </cell>
+          <cell r="B31" t="str">
+            <v>Sara</v>
+          </cell>
+          <cell r="C31" t="str">
+            <v>1405/03/30</v>
+          </cell>
+          <cell r="D31" t="str">
+            <v>1405/06/30</v>
+          </cell>
+          <cell r="E31">
+            <v>34000000</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="A32" t="str">
+            <v>HamidReza Ziayie</v>
+          </cell>
+          <cell r="B32" t="str">
+            <v>Nastaran</v>
+          </cell>
+          <cell r="C32" t="str">
+            <v>1405/03/18</v>
+          </cell>
+          <cell r="D32" t="str">
+            <v>1405/06/18</v>
+          </cell>
+          <cell r="E32">
+            <v>76000000</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="A33" t="str">
+            <v>Hamid MehraBi</v>
+          </cell>
+          <cell r="B33" t="str">
+            <v>Mohamad</v>
+          </cell>
+          <cell r="C33" t="str">
+            <v>1405/04/16</v>
+          </cell>
+          <cell r="D33" t="str">
+            <v>1405/07/16</v>
+          </cell>
+          <cell r="E33">
+            <v>60000000</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="A34" t="str">
+            <v>HonarVAr</v>
+          </cell>
+          <cell r="B34" t="str">
+            <v>Nastaran</v>
+          </cell>
+          <cell r="C34" t="str">
+            <v>1405/02/30</v>
+          </cell>
+          <cell r="D34" t="str">
+            <v>1405/05/30</v>
+          </cell>
+          <cell r="E34">
+            <v>39600000</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="A35" t="str">
+            <v>Hashem Rafie Zadeh</v>
+          </cell>
+          <cell r="B35" t="str">
+            <v>Mohamad</v>
+          </cell>
+          <cell r="C35" t="str">
+            <v>1405/04/20</v>
+          </cell>
+          <cell r="D35" t="str">
+            <v>1405/07/20</v>
+          </cell>
+          <cell r="E35">
+            <v>42900000</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="A36" t="str">
+            <v>Keyvan Rezaie</v>
+          </cell>
+          <cell r="B36" t="str">
+            <v>Naser</v>
+          </cell>
+          <cell r="C36" t="str">
+            <v>1405/05/26</v>
+          </cell>
+          <cell r="D36" t="str">
+            <v>1405/08/26</v>
+          </cell>
+          <cell r="E36">
+            <v>99000000</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="A37" t="str">
+            <v>Khashayar KhaniZadeh</v>
+          </cell>
+          <cell r="B37" t="str">
+            <v>Naser</v>
+          </cell>
+          <cell r="C37" t="str">
+            <v>1405/05/11</v>
+          </cell>
+          <cell r="D37" t="str">
+            <v>1405/08/11</v>
+          </cell>
+          <cell r="E37">
+            <v>44000000</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="A38" t="str">
+            <v>Lale Izadi</v>
+          </cell>
+          <cell r="B38" t="str">
+            <v>Sanam</v>
+          </cell>
+          <cell r="C38" t="str">
+            <v>1405/05/06</v>
+          </cell>
+          <cell r="D38" t="str">
+            <v>1405/08/06</v>
+          </cell>
+          <cell r="E38">
+            <v>80000000</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="A39" t="str">
+            <v>KIMIA Ghasemi</v>
+          </cell>
+          <cell r="B39" t="str">
+            <v>Mohamad</v>
+          </cell>
+          <cell r="C39" t="str">
+            <v>1405/05/03</v>
+          </cell>
+          <cell r="D39" t="str">
+            <v>1405/08/03</v>
+          </cell>
+          <cell r="E39">
+            <v>29700000</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="A40" t="str">
+            <v>Khatereh Jafari</v>
+          </cell>
+          <cell r="B40" t="str">
+            <v>Sanam</v>
+          </cell>
+          <cell r="C40" t="str">
+            <v>1405/04/08</v>
+          </cell>
+          <cell r="D40" t="str">
+            <v>1405/07/08</v>
+          </cell>
+          <cell r="E40">
+            <v>30000000</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="A41" t="str">
+            <v>Mansoureh AmirShahi</v>
+          </cell>
+          <cell r="B41" t="str">
+            <v>Nastaran</v>
+          </cell>
+          <cell r="C41" t="str">
+            <v>1405/06/16</v>
+          </cell>
+          <cell r="D41" t="str">
+            <v>1405/09/16</v>
+          </cell>
+          <cell r="E41">
+            <v>33000000</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="A42" t="str">
+            <v>Maasoume Zare</v>
+          </cell>
+          <cell r="B42" t="str">
+            <v>Shaqayeq</v>
+          </cell>
+          <cell r="C42" t="str">
+            <v>1405/04/28</v>
+          </cell>
+          <cell r="D42" t="str">
+            <v>1405/07/28</v>
+          </cell>
+          <cell r="E42">
+            <v>30000000</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="A43" t="str">
+            <v>Maryam Gholami</v>
+          </cell>
+          <cell r="B43" t="str">
+            <v>Mohamad</v>
+          </cell>
+          <cell r="C43" t="str">
+            <v>1405/02/16</v>
+          </cell>
+          <cell r="D43" t="str">
+            <v>1405/05/16</v>
+          </cell>
+          <cell r="E43">
+            <v>46200000</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="A44" t="str">
+            <v>Maryam DadKhah</v>
+          </cell>
+          <cell r="B44" t="str">
+            <v>Sanam</v>
+          </cell>
+          <cell r="C44" t="str">
+            <v>1405/05/27</v>
+          </cell>
+          <cell r="D44" t="str">
+            <v>1405/08/27</v>
+          </cell>
+          <cell r="E44">
+            <v>40000000</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="A45" t="str">
+            <v>Meysam Ghanbari</v>
+          </cell>
+          <cell r="B45" t="str">
+            <v>shahrzad</v>
+          </cell>
+          <cell r="C45" t="str">
+            <v>1405/05/28</v>
+          </cell>
+          <cell r="D45" t="str">
+            <v>1405/08/28</v>
+          </cell>
+          <cell r="E45">
+            <v>82500000</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="A46" t="str">
+            <v>Mazaher Hadi</v>
+          </cell>
+          <cell r="B46" t="str">
+            <v>shahrzad</v>
+          </cell>
+          <cell r="C46" t="str">
+            <v>1405/05/10</v>
+          </cell>
+          <cell r="D46" t="str">
+            <v>1405/08/10</v>
+          </cell>
+          <cell r="E46">
+            <v>58000000</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4544,8 +5351,13 @@
       <c r="F32" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="G32" s="1"/>
-      <c r="H32" s="12"/>
+      <c r="G32" s="55" t="s">
+        <v>26</v>
+      </c>
+      <c r="H32" s="12">
+        <f>VLOOKUP(A32,[1]Sheet2!A:E,5,0)</f>
+        <v>132000000</v>
+      </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
@@ -4566,8 +5378,13 @@
       <c r="F33" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="G33" s="1"/>
-      <c r="H33" s="12"/>
+      <c r="G33" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H33" s="12">
+        <f>VLOOKUP(A33,[1]Sheet2!A:E,5,0)</f>
+        <v>132000000</v>
+      </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
@@ -4588,8 +5405,13 @@
       <c r="F34" s="24" t="s">
         <v>188</v>
       </c>
-      <c r="G34" s="1"/>
-      <c r="H34" s="12"/>
+      <c r="G34" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H34" s="12">
+        <f>VLOOKUP(A34,[1]Sheet2!A:E,5,0)</f>
+        <v>55000000</v>
+      </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
@@ -4610,8 +5432,14 @@
       <c r="F35" s="25" t="s">
         <v>193</v>
       </c>
-      <c r="G35" s="1"/>
-      <c r="H35" s="12"/>
+      <c r="G35" s="1" t="str">
+        <f>VLOOKUP(A35,[1]Sheet2!A:B,2,0)</f>
+        <v>Sanam</v>
+      </c>
+      <c r="H35" s="12">
+        <f>VLOOKUP(A35,[1]Sheet2!A:E,5,0)</f>
+        <v>30600000</v>
+      </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
@@ -4654,8 +5482,14 @@
       <c r="F37" s="26" t="s">
         <v>199</v>
       </c>
-      <c r="G37" s="1"/>
-      <c r="H37" s="12"/>
+      <c r="G37" s="1" t="str">
+        <f>VLOOKUP(A37,[1]Sheet2!A:B,2,0)</f>
+        <v>Nastaran</v>
+      </c>
+      <c r="H37" s="12">
+        <f>VLOOKUP(A37,[1]Sheet2!A:E,5,0)</f>
+        <v>20000000</v>
+      </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
@@ -4676,8 +5510,14 @@
       <c r="F38" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="G38" s="1"/>
-      <c r="H38" s="12"/>
+      <c r="G38" s="1" t="str">
+        <f>VLOOKUP(A38,[1]Sheet2!A:B,2,0)</f>
+        <v>Naser</v>
+      </c>
+      <c r="H38" s="12">
+        <f>VLOOKUP(A38,[1]Sheet2!A:E,5,0)</f>
+        <v>150000000</v>
+      </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
@@ -4698,8 +5538,14 @@
       <c r="F39" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="G39" s="1"/>
-      <c r="H39" s="12"/>
+      <c r="G39" s="1" t="str">
+        <f>VLOOKUP(A39,[1]Sheet2!A:B,2,0)</f>
+        <v>Naser</v>
+      </c>
+      <c r="H39" s="12">
+        <f>VLOOKUP(A39,[1]Sheet2!A:E,5,0)</f>
+        <v>135000000</v>
+      </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
@@ -4720,8 +5566,14 @@
       <c r="F40" s="27" t="s">
         <v>222</v>
       </c>
-      <c r="G40" s="1"/>
-      <c r="H40" s="12"/>
+      <c r="G40" s="1" t="str">
+        <f>VLOOKUP(A40,[1]Sheet2!A:B,2,0)</f>
+        <v>Sanam</v>
+      </c>
+      <c r="H40" s="12">
+        <f>VLOOKUP(A40,[1]Sheet2!A:E,5,0)</f>
+        <v>60000000</v>
+      </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
@@ -4742,8 +5594,14 @@
       <c r="F41" s="25" t="s">
         <v>193</v>
       </c>
-      <c r="G41" s="1"/>
-      <c r="H41" s="12"/>
+      <c r="G41" s="1" t="str">
+        <f>VLOOKUP(A41,[1]Sheet2!A:B,2,0)</f>
+        <v>Sara</v>
+      </c>
+      <c r="H41" s="12">
+        <f>VLOOKUP(A41,[1]Sheet2!A:E,5,0)</f>
+        <v>45000000</v>
+      </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
@@ -4764,8 +5622,14 @@
       <c r="F42" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="G42" s="1"/>
-      <c r="H42" s="12"/>
+      <c r="G42" s="1" t="str">
+        <f>VLOOKUP(A42,[1]Sheet2!A:B,2,0)</f>
+        <v>Naser</v>
+      </c>
+      <c r="H42" s="12">
+        <f>VLOOKUP(A42,[1]Sheet2!A:E,5,0)</f>
+        <v>140000000</v>
+      </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
@@ -4852,8 +5716,14 @@
       <c r="F46" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="G46" s="1"/>
-      <c r="H46" s="12"/>
+      <c r="G46" s="1" t="str">
+        <f>VLOOKUP(A46,[1]Sheet2!A:B,2,0)</f>
+        <v>Sara</v>
+      </c>
+      <c r="H46" s="12">
+        <f>VLOOKUP(A46,[1]Sheet2!A:E,5,0)</f>
+        <v>27000000</v>
+      </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
@@ -5204,8 +6074,14 @@
       <c r="F62" s="34" t="s">
         <v>326</v>
       </c>
-      <c r="G62" s="1"/>
-      <c r="H62" s="12"/>
+      <c r="G62" s="1" t="str">
+        <f>VLOOKUP(A62,[1]Sheet2!A:B,2,0)</f>
+        <v>Sanam</v>
+      </c>
+      <c r="H62" s="12">
+        <f>VLOOKUP(A62,[1]Sheet2!A:E,5,0)</f>
+        <v>240000000</v>
+      </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
@@ -5226,8 +6102,14 @@
       <c r="F63" s="34" t="s">
         <v>326</v>
       </c>
-      <c r="G63" s="1"/>
-      <c r="H63" s="12"/>
+      <c r="G63" s="1" t="str">
+        <f>VLOOKUP(A63,[1]Sheet2!A:B,2,0)</f>
+        <v>Sanam</v>
+      </c>
+      <c r="H63" s="12">
+        <f>VLOOKUP(A63,[1]Sheet2!A:E,5,0)</f>
+        <v>240000000</v>
+      </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
@@ -5248,8 +6130,14 @@
       <c r="F64" s="34" t="s">
         <v>326</v>
       </c>
-      <c r="G64" s="1"/>
-      <c r="H64" s="12"/>
+      <c r="G64" s="1" t="str">
+        <f>VLOOKUP(A64,[1]Sheet2!A:B,2,0)</f>
+        <v>Sanam</v>
+      </c>
+      <c r="H64" s="12">
+        <f>VLOOKUP(A64,[1]Sheet2!A:E,5,0)</f>
+        <v>240000000</v>
+      </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
@@ -5270,8 +6158,14 @@
       <c r="F65" s="34" t="s">
         <v>326</v>
       </c>
-      <c r="G65" s="1"/>
-      <c r="H65" s="12"/>
+      <c r="G65" s="1" t="str">
+        <f>VLOOKUP(A65,[1]Sheet2!A:B,2,0)</f>
+        <v>Sanam</v>
+      </c>
+      <c r="H65" s="12">
+        <f>VLOOKUP(A65,[1]Sheet2!A:E,5,0)</f>
+        <v>240000000</v>
+      </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
@@ -5292,8 +6186,14 @@
       <c r="F66" s="34" t="s">
         <v>326</v>
       </c>
-      <c r="G66" s="1"/>
-      <c r="H66" s="12"/>
+      <c r="G66" s="1" t="str">
+        <f>VLOOKUP(A66,[1]Sheet2!A:B,2,0)</f>
+        <v>Sanam</v>
+      </c>
+      <c r="H66" s="12">
+        <f>VLOOKUP(A66,[1]Sheet2!A:E,5,0)</f>
+        <v>240000000</v>
+      </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
@@ -5314,8 +6214,14 @@
       <c r="F67" s="35" t="s">
         <v>344</v>
       </c>
-      <c r="G67" s="1"/>
-      <c r="H67" s="12"/>
+      <c r="G67" s="1" t="str">
+        <f>VLOOKUP(A67,[1]Sheet2!A:B,2,0)</f>
+        <v>Nastaran</v>
+      </c>
+      <c r="H67" s="12">
+        <f>VLOOKUP(A67,[1]Sheet2!A:E,5,0)</f>
+        <v>8800000</v>
+      </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
@@ -5336,8 +6242,14 @@
       <c r="F68" s="6" t="s">
         <v>349</v>
       </c>
-      <c r="G68" s="1"/>
-      <c r="H68" s="12"/>
+      <c r="G68" s="1" t="str">
+        <f>VLOOKUP(A68,[1]Sheet2!A:B,2,0)</f>
+        <v>Nastaran</v>
+      </c>
+      <c r="H68" s="12">
+        <f>VLOOKUP(A68,[1]Sheet2!A:E,5,0)</f>
+        <v>36000000</v>
+      </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
@@ -5380,8 +6292,14 @@
       <c r="F70" s="6" t="s">
         <v>361</v>
       </c>
-      <c r="G70" s="1"/>
-      <c r="H70" s="12"/>
+      <c r="G70" s="1" t="str">
+        <f>VLOOKUP(A70,[1]Sheet2!A:B,2,0)</f>
+        <v>Sara</v>
+      </c>
+      <c r="H70" s="12">
+        <f>VLOOKUP(A70,[1]Sheet2!A:E,5,0)</f>
+        <v>60000000</v>
+      </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
@@ -5402,8 +6320,14 @@
       <c r="F71" s="6" t="s">
         <v>361</v>
       </c>
-      <c r="G71" s="1"/>
-      <c r="H71" s="12"/>
+      <c r="G71" s="1" t="str">
+        <f>VLOOKUP(A71,[1]Sheet2!A:B,2,0)</f>
+        <v>Sara</v>
+      </c>
+      <c r="H71" s="12">
+        <f>VLOOKUP(A71,[1]Sheet2!A:E,5,0)</f>
+        <v>60000000</v>
+      </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
@@ -5424,8 +6348,14 @@
       <c r="F72" s="6" t="s">
         <v>368</v>
       </c>
-      <c r="G72" s="1"/>
-      <c r="H72" s="12"/>
+      <c r="G72" s="1" t="str">
+        <f>VLOOKUP(A72,[1]Sheet2!A:B,2,0)</f>
+        <v>Naser</v>
+      </c>
+      <c r="H72" s="12">
+        <f>VLOOKUP(A72,[1]Sheet2!A:E,5,0)</f>
+        <v>427000000</v>
+      </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
@@ -5446,8 +6376,14 @@
       <c r="F73" s="6" t="s">
         <v>368</v>
       </c>
-      <c r="G73" s="1"/>
-      <c r="H73" s="12"/>
+      <c r="G73" s="1" t="str">
+        <f>VLOOKUP(A73,[1]Sheet2!A:B,2,0)</f>
+        <v>Naser</v>
+      </c>
+      <c r="H73" s="12">
+        <f>VLOOKUP(A73,[1]Sheet2!A:E,5,0)</f>
+        <v>427000000</v>
+      </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
@@ -5468,8 +6404,14 @@
       <c r="F74" s="6" t="s">
         <v>368</v>
       </c>
-      <c r="G74" s="1"/>
-      <c r="H74" s="12"/>
+      <c r="G74" s="1" t="str">
+        <f>VLOOKUP(A74,[1]Sheet2!A:B,2,0)</f>
+        <v>Naser</v>
+      </c>
+      <c r="H74" s="12">
+        <f>VLOOKUP(A74,[1]Sheet2!A:E,5,0)</f>
+        <v>427000000</v>
+      </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
@@ -5490,8 +6432,14 @@
       <c r="F75" s="6" t="s">
         <v>380</v>
       </c>
-      <c r="G75" s="1"/>
-      <c r="H75" s="12"/>
+      <c r="G75" s="1" t="str">
+        <f>VLOOKUP(A75,[1]Sheet2!A:B,2,0)</f>
+        <v>Nastaran</v>
+      </c>
+      <c r="H75" s="12">
+        <f>VLOOKUP(A75,[1]Sheet2!A:E,5,0)</f>
+        <v>46200000</v>
+      </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
@@ -5512,8 +6460,14 @@
       <c r="F76" s="6" t="s">
         <v>380</v>
       </c>
-      <c r="G76" s="1"/>
-      <c r="H76" s="12"/>
+      <c r="G76" s="1" t="str">
+        <f>VLOOKUP(A76,[1]Sheet2!A:B,2,0)</f>
+        <v>Nastaran</v>
+      </c>
+      <c r="H76" s="12">
+        <f>VLOOKUP(A76,[1]Sheet2!A:E,5,0)</f>
+        <v>46200000</v>
+      </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
@@ -5534,8 +6488,13 @@
       <c r="F77" s="6" t="s">
         <v>388</v>
       </c>
-      <c r="G77" s="1"/>
-      <c r="H77" s="12"/>
+      <c r="G77" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H77" s="12">
+        <f>VLOOKUP(A77,[1]Sheet2!A:E,5,0)</f>
+        <v>46200000</v>
+      </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
@@ -5556,8 +6515,14 @@
       <c r="F78" s="31" t="s">
         <v>40</v>
       </c>
-      <c r="G78" s="1"/>
-      <c r="H78" s="12"/>
+      <c r="G78" s="1" t="str">
+        <f>VLOOKUP(A78,[1]Sheet2!A:B,2,0)</f>
+        <v>Sara</v>
+      </c>
+      <c r="H78" s="12">
+        <f>VLOOKUP(A78,[1]Sheet2!A:E,5,0)</f>
+        <v>75000000</v>
+      </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
@@ -5578,8 +6543,14 @@
       <c r="F79" s="31" t="s">
         <v>40</v>
       </c>
-      <c r="G79" s="1"/>
-      <c r="H79" s="12"/>
+      <c r="G79" s="1" t="str">
+        <f>VLOOKUP(A79,[1]Sheet2!A:B,2,0)</f>
+        <v>Sara</v>
+      </c>
+      <c r="H79" s="12">
+        <f>VLOOKUP(A79,[1]Sheet2!A:E,5,0)</f>
+        <v>75000000</v>
+      </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
@@ -5600,8 +6571,13 @@
       <c r="F80" s="6" t="s">
         <v>400</v>
       </c>
-      <c r="G80" s="1"/>
-      <c r="H80" s="12"/>
+      <c r="G80" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H80" s="12">
+        <f>VLOOKUP(A80,[1]Sheet2!A:E,5,0)</f>
+        <v>41580000</v>
+      </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
@@ -5622,8 +6598,13 @@
       <c r="F81" s="6" t="s">
         <v>406</v>
       </c>
-      <c r="G81" s="1"/>
-      <c r="H81" s="12"/>
+      <c r="G81" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H81" s="12">
+        <f>VLOOKUP(A81,[1]Sheet2!A:E,5,0)</f>
+        <v>6600000</v>
+      </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
@@ -5644,8 +6625,13 @@
       <c r="F82" s="6" t="s">
         <v>412</v>
       </c>
-      <c r="G82" s="1"/>
-      <c r="H82" s="12"/>
+      <c r="G82" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H82" s="12">
+        <f>VLOOKUP(A82,[1]Sheet2!A:E,5,0)</f>
+        <v>49500000</v>
+      </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
@@ -5666,8 +6652,14 @@
       <c r="F83" s="6" t="s">
         <v>418</v>
       </c>
-      <c r="G83" s="1"/>
-      <c r="H83" s="12"/>
+      <c r="G83" s="1" t="str">
+        <f>VLOOKUP(A83,[1]Sheet2!A:B,2,0)</f>
+        <v>Nastaran</v>
+      </c>
+      <c r="H83" s="12">
+        <f>VLOOKUP(A83,[1]Sheet2!A:E,5,0)</f>
+        <v>33000000</v>
+      </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
@@ -5688,8 +6680,14 @@
       <c r="F84" s="6" t="s">
         <v>424</v>
       </c>
-      <c r="G84" s="1"/>
-      <c r="H84" s="12"/>
+      <c r="G84" s="1" t="str">
+        <f>VLOOKUP(A84,[1]Sheet2!A:B,2,0)</f>
+        <v>Nastaran</v>
+      </c>
+      <c r="H84" s="12">
+        <f>VLOOKUP(A84,[1]Sheet2!A:E,5,0)</f>
+        <v>23100000</v>
+      </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
@@ -5710,8 +6708,14 @@
       <c r="F85" s="6" t="s">
         <v>424</v>
       </c>
-      <c r="G85" s="1"/>
-      <c r="H85" s="12"/>
+      <c r="G85" s="1" t="str">
+        <f>VLOOKUP(A85,[1]Sheet2!A:B,2,0)</f>
+        <v>Nastaran</v>
+      </c>
+      <c r="H85" s="12">
+        <f>VLOOKUP(A85,[1]Sheet2!A:E,5,0)</f>
+        <v>23100000</v>
+      </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
@@ -5732,8 +6736,13 @@
       <c r="F86" s="6" t="s">
         <v>433</v>
       </c>
-      <c r="G86" s="1"/>
-      <c r="H86" s="12"/>
+      <c r="G86" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H86" s="12">
+        <f>VLOOKUP(A86,[1]Sheet2!A:E,5,0)</f>
+        <v>30000000</v>
+      </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
@@ -5776,8 +6785,14 @@
       <c r="F88" s="6" t="s">
         <v>445</v>
       </c>
-      <c r="G88" s="1"/>
-      <c r="H88" s="12"/>
+      <c r="G88" s="1" t="str">
+        <f>VLOOKUP(A88,[1]Sheet2!A:B,2,0)</f>
+        <v>Nastaran</v>
+      </c>
+      <c r="H88" s="12">
+        <f>VLOOKUP(A88,[1]Sheet2!A:E,5,0)</f>
+        <v>170000000</v>
+      </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
@@ -5798,8 +6813,14 @@
       <c r="F89" s="6" t="s">
         <v>445</v>
       </c>
-      <c r="G89" s="1"/>
-      <c r="H89" s="12"/>
+      <c r="G89" s="1" t="str">
+        <f>VLOOKUP(A89,[1]Sheet2!A:B,2,0)</f>
+        <v>Nastaran</v>
+      </c>
+      <c r="H89" s="12">
+        <f>VLOOKUP(A89,[1]Sheet2!A:E,5,0)</f>
+        <v>170000000</v>
+      </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
@@ -5864,8 +6885,14 @@
       <c r="F92" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="G92" s="1"/>
-      <c r="H92" s="12"/>
+      <c r="G92" s="1" t="str">
+        <f>VLOOKUP(A92,[1]Sheet2!A:B,2,0)</f>
+        <v>Nastaran</v>
+      </c>
+      <c r="H92" s="12">
+        <f>VLOOKUP(A92,[1]Sheet2!A:E,5,0)</f>
+        <v>6600000</v>
+      </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
@@ -5886,8 +6913,14 @@
       <c r="F93" s="6" t="s">
         <v>467</v>
       </c>
-      <c r="G93" s="1"/>
-      <c r="H93" s="12"/>
+      <c r="G93" s="1" t="str">
+        <f>VLOOKUP(A93,[1]Sheet2!A:B,2,0)</f>
+        <v>Nastaran</v>
+      </c>
+      <c r="H93" s="12">
+        <f>VLOOKUP(A93,[1]Sheet2!A:E,5,0)</f>
+        <v>72600000</v>
+      </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
@@ -5908,8 +6941,14 @@
       <c r="F94" s="36" t="s">
         <v>472</v>
       </c>
-      <c r="G94" s="1"/>
-      <c r="H94" s="12"/>
+      <c r="G94" s="1" t="str">
+        <f>VLOOKUP(A94,[1]Sheet2!A:B,2,0)</f>
+        <v>Nastaran</v>
+      </c>
+      <c r="H94" s="12">
+        <f>VLOOKUP(A94,[1]Sheet2!A:E,5,0)</f>
+        <v>49500000</v>
+      </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
@@ -5930,8 +6969,14 @@
       <c r="F95" s="28" t="s">
         <v>255</v>
       </c>
-      <c r="G95" s="1"/>
-      <c r="H95" s="12"/>
+      <c r="G95" s="1" t="str">
+        <f>VLOOKUP(A95,[1]Sheet2!A:B,2,0)</f>
+        <v>Sara</v>
+      </c>
+      <c r="H95" s="12">
+        <f>VLOOKUP(A95,[1]Sheet2!A:E,5,0)</f>
+        <v>34000000</v>
+      </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
@@ -5974,8 +7019,14 @@
       <c r="F97" s="6" t="s">
         <v>487</v>
       </c>
-      <c r="G97" s="1"/>
-      <c r="H97" s="12"/>
+      <c r="G97" s="1" t="str">
+        <f>VLOOKUP(A97,[1]Sheet2!A:B,2,0)</f>
+        <v>Naser</v>
+      </c>
+      <c r="H97" s="12">
+        <f>VLOOKUP(A97,[1]Sheet2!A:E,5,0)</f>
+        <v>206000000</v>
+      </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
@@ -5996,8 +7047,14 @@
       <c r="F98" s="6" t="s">
         <v>487</v>
       </c>
-      <c r="G98" s="1"/>
-      <c r="H98" s="12"/>
+      <c r="G98" s="1" t="str">
+        <f>VLOOKUP(A98,[1]Sheet2!A:B,2,0)</f>
+        <v>Naser</v>
+      </c>
+      <c r="H98" s="12">
+        <f>VLOOKUP(A98,[1]Sheet2!A:E,5,0)</f>
+        <v>206000000</v>
+      </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
@@ -6018,8 +7075,13 @@
       <c r="F99" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="G99" s="1"/>
-      <c r="H99" s="12"/>
+      <c r="G99" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H99" s="12">
+        <f>VLOOKUP(A99,[1]Sheet2!A:E,5,0)</f>
+        <v>60000000</v>
+      </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
@@ -6040,8 +7102,14 @@
       <c r="F100" s="37" t="s">
         <v>500</v>
       </c>
-      <c r="G100" s="1"/>
-      <c r="H100" s="12"/>
+      <c r="G100" s="1" t="str">
+        <f>VLOOKUP(A100,[1]Sheet2!A:B,2,0)</f>
+        <v>Nastaran</v>
+      </c>
+      <c r="H100" s="12">
+        <f>VLOOKUP(A100,[1]Sheet2!A:E,5,0)</f>
+        <v>76000000</v>
+      </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
@@ -6062,8 +7130,13 @@
       <c r="F101" s="38" t="s">
         <v>505</v>
       </c>
-      <c r="G101" s="1"/>
-      <c r="H101" s="12"/>
+      <c r="G101" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H101" s="12">
+        <f>VLOOKUP(A101,[1]Sheet2!A:E,5,0)</f>
+        <v>42900000</v>
+      </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
@@ -6084,8 +7157,14 @@
       <c r="F102" s="6" t="s">
         <v>511</v>
       </c>
-      <c r="G102" s="1"/>
-      <c r="H102" s="12"/>
+      <c r="G102" s="1" t="str">
+        <f>VLOOKUP(A102,[1]Sheet2!A:B,2,0)</f>
+        <v>Nastaran</v>
+      </c>
+      <c r="H102" s="12">
+        <f>VLOOKUP(A102,[1]Sheet2!A:E,5,0)</f>
+        <v>39600000</v>
+      </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
@@ -6370,8 +7449,14 @@
       <c r="F115" s="6" t="s">
         <v>510</v>
       </c>
-      <c r="G115" s="1"/>
-      <c r="H115" s="12"/>
+      <c r="G115" s="1" t="str">
+        <f>VLOOKUP(A115,[1]Sheet2!A:B,2,0)</f>
+        <v>Naser</v>
+      </c>
+      <c r="H115" s="12">
+        <f>VLOOKUP(A115,[1]Sheet2!A:E,5,0)</f>
+        <v>99000000</v>
+      </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
@@ -6392,8 +7477,14 @@
       <c r="F116" s="6" t="s">
         <v>510</v>
       </c>
-      <c r="G116" s="1"/>
-      <c r="H116" s="12"/>
+      <c r="G116" s="1" t="str">
+        <f>VLOOKUP(A116,[1]Sheet2!A:B,2,0)</f>
+        <v>Naser</v>
+      </c>
+      <c r="H116" s="12">
+        <f>VLOOKUP(A116,[1]Sheet2!A:E,5,0)</f>
+        <v>99000000</v>
+      </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
@@ -6414,8 +7505,14 @@
       <c r="F117" s="6" t="s">
         <v>510</v>
       </c>
-      <c r="G117" s="1"/>
-      <c r="H117" s="12"/>
+      <c r="G117" s="1" t="str">
+        <f>VLOOKUP(A117,[1]Sheet2!A:B,2,0)</f>
+        <v>Naser</v>
+      </c>
+      <c r="H117" s="12">
+        <f>VLOOKUP(A117,[1]Sheet2!A:E,5,0)</f>
+        <v>99000000</v>
+      </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
@@ -6436,8 +7533,14 @@
       <c r="F118" s="13" t="s">
         <v>571</v>
       </c>
-      <c r="G118" s="1"/>
-      <c r="H118" s="12"/>
+      <c r="G118" s="1" t="str">
+        <f>VLOOKUP(A118,[1]Sheet2!A:B,2,0)</f>
+        <v>Naser</v>
+      </c>
+      <c r="H118" s="12">
+        <f>VLOOKUP(A118,[1]Sheet2!A:E,5,0)</f>
+        <v>44000000</v>
+      </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
@@ -6458,8 +7561,14 @@
       <c r="F119" s="6" t="s">
         <v>576</v>
       </c>
-      <c r="G119" s="1"/>
-      <c r="H119" s="12"/>
+      <c r="G119" s="1" t="str">
+        <f>VLOOKUP(A119,[1]Sheet2!A:B,2,0)</f>
+        <v>Sanam</v>
+      </c>
+      <c r="H119" s="12">
+        <f>VLOOKUP(A119,[1]Sheet2!A:E,5,0)</f>
+        <v>30000000</v>
+      </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
@@ -6480,8 +7589,13 @@
       <c r="F120" s="6" t="s">
         <v>582</v>
       </c>
-      <c r="G120" s="1"/>
-      <c r="H120" s="12"/>
+      <c r="G120" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H120" s="12">
+        <f>VLOOKUP(A120,[1]Sheet2!A:E,5,0)</f>
+        <v>29700000</v>
+      </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
@@ -6502,8 +7616,14 @@
       <c r="F121" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="G121" s="1"/>
-      <c r="H121" s="12"/>
+      <c r="G121" s="1" t="str">
+        <f>VLOOKUP(A121,[1]Sheet2!A:B,2,0)</f>
+        <v>Sanam</v>
+      </c>
+      <c r="H121" s="12">
+        <f>VLOOKUP(A121,[1]Sheet2!A:E,5,0)</f>
+        <v>80000000</v>
+      </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
@@ -6524,8 +7644,13 @@
       <c r="F122" s="41" t="s">
         <v>591</v>
       </c>
-      <c r="G122" s="1"/>
-      <c r="H122" s="12"/>
+      <c r="G122" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H122" s="12">
+        <f>VLOOKUP(A122,[1]Sheet2!A:E,5,0)</f>
+        <v>30000000</v>
+      </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
@@ -6568,8 +7693,14 @@
       <c r="F124" s="32" t="s">
         <v>304</v>
       </c>
-      <c r="G124" s="1"/>
-      <c r="H124" s="12"/>
+      <c r="G124" s="1" t="str">
+        <f>VLOOKUP(A124,[1]Sheet2!A:B,2,0)</f>
+        <v>Nastaran</v>
+      </c>
+      <c r="H124" s="12">
+        <f>VLOOKUP(A124,[1]Sheet2!A:E,5,0)</f>
+        <v>33000000</v>
+      </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
@@ -6590,8 +7721,14 @@
       <c r="F125" s="26" t="s">
         <v>199</v>
       </c>
-      <c r="G125" s="1"/>
-      <c r="H125" s="12"/>
+      <c r="G125" s="1" t="str">
+        <f>VLOOKUP(A125,[1]Sheet2!A:B,2,0)</f>
+        <v>Sanam</v>
+      </c>
+      <c r="H125" s="12">
+        <f>VLOOKUP(A125,[1]Sheet2!A:E,5,0)</f>
+        <v>40000000</v>
+      </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
@@ -6612,8 +7749,13 @@
       <c r="F126" s="6" t="s">
         <v>607</v>
       </c>
-      <c r="G126" s="1"/>
-      <c r="H126" s="12"/>
+      <c r="G126" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H126" s="12">
+        <f>VLOOKUP(A126,[1]Sheet2!A:E,5,0)</f>
+        <v>46200000</v>
+      </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
@@ -6656,8 +7798,13 @@
       <c r="F128" s="6" t="s">
         <v>618</v>
       </c>
-      <c r="G128" s="1"/>
-      <c r="H128" s="12"/>
+      <c r="G128" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H128" s="12">
+        <f>VLOOKUP(A128,[1]Sheet2!A:E,5,0)</f>
+        <v>58000000</v>
+      </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A129" s="1" t="s">
@@ -6700,8 +7847,13 @@
       <c r="F130" s="6" t="s">
         <v>624</v>
       </c>
-      <c r="G130" s="1"/>
-      <c r="H130" s="12"/>
+      <c r="G130" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H130" s="12">
+        <f>VLOOKUP(A130,[1]Sheet2!A:E,5,0)</f>
+        <v>82500000</v>
+      </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="s">
@@ -6722,8 +7874,13 @@
       <c r="F131" s="6" t="s">
         <v>624</v>
       </c>
-      <c r="G131" s="1"/>
-      <c r="H131" s="12"/>
+      <c r="G131" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H131" s="12">
+        <f>VLOOKUP(A131,[1]Sheet2!A:E,5,0)</f>
+        <v>82500000</v>
+      </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
@@ -6744,8 +7901,13 @@
       <c r="F132" s="6" t="s">
         <v>624</v>
       </c>
-      <c r="G132" s="1"/>
-      <c r="H132" s="12"/>
+      <c r="G132" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H132" s="12">
+        <f>VLOOKUP(A132,[1]Sheet2!A:E,5,0)</f>
+        <v>82500000</v>
+      </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A133" s="1" t="s">

--- a/Campaigns_Master.xlsx
+++ b/Campaigns_Master.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Good KoDz\Banner Monitor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4CE86CC-04F4-4110-A083-6F72CFC43DB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2EEE659-7131-47F5-8F73-3D86EB815B3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EBB7D5F9-BF11-4273-8F7B-7CCC7D024DDF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-  </externalReferences>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$217</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1343" uniqueCount="984">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1321" uniqueCount="893">
   <si>
     <t>Campaign Name</t>
   </si>
@@ -668,12 +668,6 @@
     <t>https://adserver.doctoreto.com/www/images/1b3c57ec008a30b74d0946a4e88f8891.webp</t>
   </si>
   <si>
-    <t>1404/11/26</t>
-  </si>
-  <si>
-    <t>1405/02/26</t>
-  </si>
-  <si>
     <t>Dr Atefe Faramarzi</t>
   </si>
   <si>
@@ -704,12 +698,6 @@
     <t>https://adserver.doctoreto.com/www/images/d9e092b9849657c181499a8c1465a8b6.gif</t>
   </si>
   <si>
-    <t>1405/03/31</t>
-  </si>
-  <si>
-    <t>1405/06/31</t>
-  </si>
-  <si>
     <t>Dr Azadeh MirMaasoumi</t>
   </si>
   <si>
@@ -743,12 +731,6 @@
     <t>https://adserver.doctoreto.com/www/images/5a8a180938f71ebad3b66da5746c3967.webp</t>
   </si>
   <si>
-    <t>1404/10/16</t>
-  </si>
-  <si>
-    <t>1405/01/16</t>
-  </si>
-  <si>
     <t>DR Farzane FereyDouni</t>
   </si>
   <si>
@@ -770,12 +752,6 @@
     <t>https://adserver.doctoreto.com/www/images/ca7b896b810161850c22621bf576f2ba.webp</t>
   </si>
   <si>
-    <t>1404/10/06</t>
-  </si>
-  <si>
-    <t>1405/01/06</t>
-  </si>
-  <si>
     <t>Dr Homa Sharifi</t>
   </si>
   <si>
@@ -785,12 +761,6 @@
     <t>https://adserver.doctoreto.com/www/images/41545108844e6cc1bb058d658a970dab.webp</t>
   </si>
   <si>
-    <t>1404/10/14</t>
-  </si>
-  <si>
-    <t>1405/01/14</t>
-  </si>
-  <si>
     <t>Dr Hossein AdlKhoo</t>
   </si>
   <si>
@@ -821,9 +791,6 @@
     <t>https://adserver.doctoreto.com/www/images/9acd5b90ded12d8d2c28cc0928552dce.webp</t>
   </si>
   <si>
-    <t>1405/02/14</t>
-  </si>
-  <si>
     <t>Dr Khosrow Barkhordari</t>
   </si>
   <si>
@@ -893,12 +860,6 @@
     <t>https://adserver.doctoreto.com/www/images/fee1fa2e2b40ed1ad36e3326adea3df0.gif</t>
   </si>
   <si>
-    <t>1405/02/22</t>
-  </si>
-  <si>
-    <t>1405/05/22</t>
-  </si>
-  <si>
     <t>Dr Maryam Izadi</t>
   </si>
   <si>
@@ -920,12 +881,6 @@
     <t>https://adserver.doctoreto.com/www/images/8780a5332e132d11047fbc9d2566f467.webp</t>
   </si>
   <si>
-    <t>1404/10/30</t>
-  </si>
-  <si>
-    <t>1405/01/30</t>
-  </si>
-  <si>
     <t>Dr MirBoLook</t>
   </si>
   <si>
@@ -1085,12 +1040,6 @@
     <t>https://adserver.doctoreto.com/www/images/251cdf23749268b803256fb13fedff63.webp</t>
   </si>
   <si>
-    <t>1404/05/07</t>
-  </si>
-  <si>
-    <t>1404/08/07</t>
-  </si>
-  <si>
     <t>Dr. Fahime Bayati</t>
   </si>
   <si>
@@ -1103,12 +1052,6 @@
     <t>https://adserver.doctoreto.com/www/images/d00c38b99ee55b393cb35ee0d778a098.webp</t>
   </si>
   <si>
-    <t>1404/07/22</t>
-  </si>
-  <si>
-    <t>1404/10/22</t>
-  </si>
-  <si>
     <t>Dr. Farshad Sadeghi</t>
   </si>
   <si>
@@ -1121,12 +1064,6 @@
     <t>https://adserver.doctoreto.com/www/images/7af43c5e49af60fad159b22d8bfb4e68.webp</t>
   </si>
   <si>
-    <t>1404/09/01</t>
-  </si>
-  <si>
-    <t>1404/12/01</t>
-  </si>
-  <si>
     <t>https://adserver.doctoreto.com/www/delivery/cl.php?bannerid=460&amp;zoneid=0&amp;log=no&amp;sig=182da98e8fa9d0ecfc9869b05147fde42a0dd8c2ae889d5b292b1a62b05db724&amp;dest=https%3A%2F%2Fdoctoreto.com%2Fdoctor%2Fdr-farshad-sadeghi%2FZpjLPG</t>
   </si>
   <si>
@@ -1142,12 +1079,6 @@
     <t>https://adserver.doctoreto.com/www/images/149c8fcf96bd0ff6fbebf7d2ff6dae06.png</t>
   </si>
   <si>
-    <t>1403/07/16</t>
-  </si>
-  <si>
-    <t>1403/10/16</t>
-  </si>
-  <si>
     <t>Dr. Ghazi Mobile</t>
   </si>
   <si>
@@ -1178,12 +1109,6 @@
     <t>https://adserver.doctoreto.com/www/images/ecd2425596cd95ce65a4958b4088cd86.gif</t>
   </si>
   <si>
-    <t>1404/05/04</t>
-  </si>
-  <si>
-    <t>1404/08/04</t>
-  </si>
-  <si>
     <t>https://adserver.doctoreto.com/www/delivery/cl.php?bannerid=368&amp;zoneid=0&amp;log=no&amp;sig=76ad1b47abf3aa99b04bd2e485763cac1ac9b7c98cc5bea2c5a22354835804be&amp;dest=https%3A%2F%2Fdoctoreto.com%2Fdoctor%2Fdr-mohammad-hadi-mansoori%2FGQDpDq</t>
   </si>
   <si>
@@ -1202,12 +1127,6 @@
     <t>https://adserver.doctoreto.com/www/images/5b7721bab09cb3a8221553f7fddeb69e.gif</t>
   </si>
   <si>
-    <t>1403/06/24</t>
-  </si>
-  <si>
-    <t>1403/09/24</t>
-  </si>
-  <si>
     <t>Dr. Izadpanah</t>
   </si>
   <si>
@@ -1238,12 +1157,6 @@
     <t>https://adserver.doctoreto.com/www/images/298541812074c841525b6d7e68dfc2fa.webp</t>
   </si>
   <si>
-    <t>1404/05/22</t>
-  </si>
-  <si>
-    <t>1404/08/22</t>
-  </si>
-  <si>
     <t>Dr. Mayryam Farokhshahi</t>
   </si>
   <si>
@@ -1256,12 +1169,6 @@
     <t>https://adserver.doctoreto.com/www/images/08cd30b6bee19b3810448f15deee3152.webp</t>
   </si>
   <si>
-    <t>1404/08/13</t>
-  </si>
-  <si>
-    <t>1404/11/13</t>
-  </si>
-  <si>
     <t>Dr. Mohammad Borzoyi</t>
   </si>
   <si>
@@ -1274,12 +1181,6 @@
     <t>https://adserver.doctoreto.com/www/images/1074737291b02332e0d2549f3637eff4.webp</t>
   </si>
   <si>
-    <t>1404/05/27</t>
-  </si>
-  <si>
-    <t>1404/08/27</t>
-  </si>
-  <si>
     <t>Dr. Natami</t>
   </si>
   <si>
@@ -1292,12 +1193,6 @@
     <t>https://adserver.doctoreto.com/www/images/9c9afdc6be66c7d21fcd31dd6cc0794d.webp</t>
   </si>
   <si>
-    <t>1404/03/25</t>
-  </si>
-  <si>
-    <t>1404/06/25</t>
-  </si>
-  <si>
     <t>Dr. Negin Asna Asahari</t>
   </si>
   <si>
@@ -1310,12 +1205,6 @@
     <t>https://adserver.doctoreto.com/www/images/b64bd0c5274d29023c23dc47c572bc1e.webp</t>
   </si>
   <si>
-    <t>1403/12/21</t>
-  </si>
-  <si>
-    <t>1404/03/21</t>
-  </si>
-  <si>
     <t>Dr. Asna Asahari</t>
   </si>
   <si>
@@ -1337,12 +1226,6 @@
     <t>https://adserver.doctoreto.com/www/images/4177dc12f0638bcb5ca37cb9f298546e.webp</t>
   </si>
   <si>
-    <t>1404/09/09</t>
-  </si>
-  <si>
-    <t>1404/12/09</t>
-  </si>
-  <si>
     <t>Dr. Sara Feiz</t>
   </si>
   <si>
@@ -1355,12 +1238,6 @@
     <t>https://adserver.doctoreto.com/www/images/b3b2d4333af6b6d30d7fa7fafdd6f63a.webp</t>
   </si>
   <si>
-    <t>1404/02/01</t>
-  </si>
-  <si>
-    <t>1404/05/01</t>
-  </si>
-  <si>
     <t>Dr. YazdanShenas</t>
   </si>
   <si>
@@ -1373,12 +1250,6 @@
     <t>https://adserver.doctoreto.com/www/images/cd5f7537e03353c6c4bc0bf44547f410.gif</t>
   </si>
   <si>
-    <t>1402/12/08</t>
-  </si>
-  <si>
-    <t>1403/03/08</t>
-  </si>
-  <si>
     <t>Dr. Yazdan Shenas</t>
   </si>
   <si>
@@ -1400,12 +1271,6 @@
     <t>https://adserver.doctoreto.com/www/images/0cb9efe2abd2a105e5dc0513bb6bf296.webp</t>
   </si>
   <si>
-    <t>1403/08/02</t>
-  </si>
-  <si>
-    <t>1403/11/02</t>
-  </si>
-  <si>
     <t>Energy physiotherapy Clinic</t>
   </si>
   <si>
@@ -1427,9 +1292,6 @@
     <t>https://adserver.doctoreto.com/www/images/7395d17bf626911ab67acb9ded0dbf97.gif</t>
   </si>
   <si>
-    <t>1405/01/23</t>
-  </si>
-  <si>
     <t>Farzane Mortazavi Far</t>
   </si>
   <si>
@@ -1439,12 +1301,6 @@
     <t>https://adserver.doctoreto.com/www/images/9af22b1ec2a7d650756283aac18dd812.gif</t>
   </si>
   <si>
-    <t>1405/01/26</t>
-  </si>
-  <si>
-    <t>1405/04/26</t>
-  </si>
-  <si>
     <t>Farzin Khorvash</t>
   </si>
   <si>
@@ -1481,9 +1337,6 @@
     <t>https://adserver.doctoreto.com/www/images/476f0b249b6c571ce8c1a90853846a8d.gif</t>
   </si>
   <si>
-    <t>1404/12/25</t>
-  </si>
-  <si>
     <t>1405/03/25</t>
   </si>
   <si>
@@ -1499,9 +1352,6 @@
     <t>https://adserver.doctoreto.com/www/images/505ff2245b1754ae6d702fab2bae6ebb.gif</t>
   </si>
   <si>
-    <t>1405/02/20</t>
-  </si>
-  <si>
     <t>1405/05/20</t>
   </si>
   <si>
@@ -1538,12 +1388,6 @@
     <t>https://adserver.doctoreto.com/www/images/b051c441a1a2161ebdf5272adea90c60.gif</t>
   </si>
   <si>
-    <t>1405/03/23</t>
-  </si>
-  <si>
-    <t>1405/06/23</t>
-  </si>
-  <si>
     <t>Hashem Rafie Zadeh</t>
   </si>
   <si>
@@ -1571,12 +1415,6 @@
     <t>https://adserver.doctoreto.com/www/images/58e1b0fdd6843b630c06a11efd57e81c.gif</t>
   </si>
   <si>
-    <t>1405/03/05</t>
-  </si>
-  <si>
-    <t>1405/06/05</t>
-  </si>
-  <si>
     <t>Iran e Pak</t>
   </si>
   <si>
@@ -1613,12 +1451,6 @@
     <t>https://adserver.doctoreto.com/www/images/9949ebd2565ab00772672f4bef400f43.gif</t>
   </si>
   <si>
-    <t>1405/02/23</t>
-  </si>
-  <si>
-    <t>1405/05/23</t>
-  </si>
-  <si>
     <t>Asab o Ravan PLP - Janbaz 1405</t>
   </si>
   <si>
@@ -1703,12 +1535,6 @@
     <t>https://adserver.doctoreto.com/www/images/bf2a8f831953dba9dd16ef40880ca7ce.gif</t>
   </si>
   <si>
-    <t>1405/05/14</t>
-  </si>
-  <si>
-    <t>1405/08/14</t>
-  </si>
-  <si>
     <t>Keyvan Rezaie</t>
   </si>
   <si>
@@ -1721,9 +1547,6 @@
     <t>https://adserver.doctoreto.com/www/images/acde2996db595be67005e7e501acb22b.gif</t>
   </si>
   <si>
-    <t>1404/12/05</t>
-  </si>
-  <si>
     <t>Dr K1 REza Mobile</t>
   </si>
   <si>
@@ -1766,12 +1589,6 @@
     <t>https://adserver.doctoreto.com/www/images/8f32e8c82dd07ac941b5cc1e4753ec54.gif</t>
   </si>
   <si>
-    <t>1405/02/02</t>
-  </si>
-  <si>
-    <t>1405/05/02</t>
-  </si>
-  <si>
     <t>KIMIA Ghasemi</t>
   </si>
   <si>
@@ -1784,12 +1601,6 @@
     <t>https://adserver.doctoreto.com/www/images/92e5713fc40deec20985a031b6ccf7d8.webp</t>
   </si>
   <si>
-    <t>1405/02/01</t>
-  </si>
-  <si>
-    <t>1405/05/01</t>
-  </si>
-  <si>
     <t>Lale Izadi</t>
   </si>
   <si>
@@ -1826,9 +1637,6 @@
     <t>https://adserver.doctoreto.com/www/images/bb89509d4674ed40990795340326499d.gif</t>
   </si>
   <si>
-    <t>1405/02/12</t>
-  </si>
-  <si>
     <t>Mansoureh AmirShahi</t>
   </si>
   <si>
@@ -1877,12 +1685,6 @@
     <t>https://adserver.doctoreto.com/www/images/f1184ebf402505b47bb3ca528fea816f.gif</t>
   </si>
   <si>
-    <t>1404/12/28</t>
-  </si>
-  <si>
-    <t>1405/03/28</t>
-  </si>
-  <si>
     <t>Mazaher Hadi</t>
   </si>
   <si>
@@ -1892,12 +1694,6 @@
     <t>https://adserver.doctoreto.com/www/images/730b0b149022a1c9b8f4b04bfc672be3.webp</t>
   </si>
   <si>
-    <t>1404/12/02</t>
-  </si>
-  <si>
-    <t>1405/03/02</t>
-  </si>
-  <si>
     <t>Mehdi RismanChian</t>
   </si>
   <si>
@@ -1910,12 +1706,6 @@
     <t>https://adserver.doctoreto.com/www/images/b6233ba110dd29711cf9bd347709f9c8.gif</t>
   </si>
   <si>
-    <t>1405/02/08</t>
-  </si>
-  <si>
-    <t>1405/05/08</t>
-  </si>
-  <si>
     <t>Meysam Ghanbari</t>
   </si>
   <si>
@@ -1982,12 +1772,6 @@
     <t>https://adserver.doctoreto.com/www/images/56bab9ebc1ecc5a721f099564b49b5cc.gif</t>
   </si>
   <si>
-    <t>1405/05/07</t>
-  </si>
-  <si>
-    <t>1405/08/07</t>
-  </si>
-  <si>
     <t>Mirozh Center</t>
   </si>
   <si>
@@ -1997,12 +1781,6 @@
     <t>https://adserver.doctoreto.com/www/images/04f4a15d108615ca774dd50da159a53d.gif</t>
   </si>
   <si>
-    <t>1405/03/12</t>
-  </si>
-  <si>
-    <t>1405/06/12</t>
-  </si>
-  <si>
     <t>Mohammad Aria Sadr</t>
   </si>
   <si>
@@ -2048,12 +1826,6 @@
     <t>https://adserver.doctoreto.com/www/images/a3f3abd82902c1efcc76c75290d8d47e.webp</t>
   </si>
   <si>
-    <t>1404/11/27</t>
-  </si>
-  <si>
-    <t>1405/02/27</t>
-  </si>
-  <si>
     <t>Mohammmad Javad Bagheri 02</t>
   </si>
   <si>
@@ -2084,12 +1856,6 @@
     <t>https://adserver.doctoreto.com/www/images/b653ed1bbbbfe705b69bdea0e2d2b8de.gif</t>
   </si>
   <si>
-    <t>1405/05/18</t>
-  </si>
-  <si>
-    <t>1405/08/18</t>
-  </si>
-  <si>
     <t>My Lady</t>
   </si>
   <si>
@@ -2102,9 +1868,6 @@
     <t>https://adserver.doctoreto.com/www/images/086bb7c6a74c0b4438c77d55980cca1a.png</t>
   </si>
   <si>
-    <t>1405/03/07</t>
-  </si>
-  <si>
     <t>Parastoo AshTiJoo</t>
   </si>
   <si>
@@ -2135,12 +1898,6 @@
     <t>https://adserver.doctoreto.com/www/images/0c363234214fa29bc6149830e7b83644.webp</t>
   </si>
   <si>
-    <t>1402/11/29</t>
-  </si>
-  <si>
-    <t>1403/02/29</t>
-  </si>
-  <si>
     <t>pourSina Clinic</t>
   </si>
   <si>
@@ -2180,9 +1937,6 @@
     <t>https://adserver.doctoreto.com/www/images/a96cf8bbdce3f31e57e41be6dac9cea3.webp</t>
   </si>
   <si>
-    <t>1404/06/09</t>
-  </si>
-  <si>
     <t>Reyhane Seraj</t>
   </si>
   <si>
@@ -2192,12 +1946,6 @@
     <t>https://adserver.doctoreto.com/www/images/53da9a43f5c1e258cd9b7b00204242ce.gif</t>
   </si>
   <si>
-    <t>1405/02/15</t>
-  </si>
-  <si>
-    <t>1405/05/15</t>
-  </si>
-  <si>
     <t>Sahami Clinic</t>
   </si>
   <si>
@@ -2300,9 +2048,6 @@
     <t>https://adserver.doctoreto.com/www/images/0bf67b530b49e75a37268e73ba01c2dd.gif</t>
   </si>
   <si>
-    <t>1405/01/29</t>
-  </si>
-  <si>
     <t>SamaNeh HamzLou</t>
   </si>
   <si>
@@ -2345,9 +2090,6 @@
     <t>https://adserver.doctoreto.com/www/images/f363916387decab619902e1161434020.gif</t>
   </si>
   <si>
-    <t>1405/07/23</t>
-  </si>
-  <si>
     <t>Samira Mesbah Clinic Mobile</t>
   </si>
   <si>
@@ -2378,12 +2120,6 @@
     <t>https://adserver.doctoreto.com/www/images/e1ef75dc2f801aa5a357b8886f69cc5d.webp</t>
   </si>
   <si>
-    <t>1403/10/15</t>
-  </si>
-  <si>
-    <t>1404/01/15</t>
-  </si>
-  <si>
     <t>Sepamed Clinc</t>
   </si>
   <si>
@@ -2483,12 +2219,6 @@
     <t>https://adserver.doctoreto.com/www/images/321e2d52ff0dd1aec02c52a6c4fa4bbb.gif</t>
   </si>
   <si>
-    <t>1405/04/21</t>
-  </si>
-  <si>
-    <t>1405/07/21</t>
-  </si>
-  <si>
     <t>Shahriar Azizi</t>
   </si>
   <si>
@@ -2537,9 +2267,6 @@
     <t>https://adserver.doctoreto.com/www/images/bad5bc5b3f6788bd9f8595fd58301af2.webp</t>
   </si>
   <si>
-    <t>1405/03/11</t>
-  </si>
-  <si>
     <t>1405/06/11</t>
   </si>
   <si>
@@ -2633,12 +2360,6 @@
     <t>https://adserver.doctoreto.com/www/images/10a494ead3f9b4ad3ec9f7c25af544ea.gif</t>
   </si>
   <si>
-    <t>1405/03/13</t>
-  </si>
-  <si>
-    <t>1405/06/13</t>
-  </si>
-  <si>
     <t>Dr - Amine davoodian</t>
   </si>
   <si>
@@ -2720,12 +2441,6 @@
     <t>https://adserver.doctoreto.com/www/images/1a4b661b62075cb19c756f13c1da9b85.webp</t>
   </si>
   <si>
-    <t>1404/08/05</t>
-  </si>
-  <si>
-    <t>1404/11/05</t>
-  </si>
-  <si>
     <t>Dr. Arezo Omidbar khoda</t>
   </si>
   <si>
@@ -2738,12 +2453,6 @@
     <t>https://adserver.doctoreto.com/www/images/a22e6444f6635212bba97f25b22bac1a.webp</t>
   </si>
   <si>
-    <t>1404/09/04</t>
-  </si>
-  <si>
-    <t>1404/12/04</t>
-  </si>
-  <si>
     <t>Dr. Arezo Omidvarkhoda</t>
   </si>
   <si>
@@ -2765,12 +2474,6 @@
     <t>https://adserver.doctoreto.com/www/images/dcaf24a6e931f7c291b6ef8b9b9eae61.webp</t>
   </si>
   <si>
-    <t>1404/08/10</t>
-  </si>
-  <si>
-    <t>1404/11/10</t>
-  </si>
-  <si>
     <t>Dr. Farzad Noori</t>
   </si>
   <si>
@@ -2780,9 +2483,6 @@
     <t>https://adserver.doctoreto.com/www/images/cc7d877743d894f645f0aa864d87d4b3.webp</t>
   </si>
   <si>
-    <t>1404/11/07</t>
-  </si>
-  <si>
     <t>Dr. Goshaderoo</t>
   </si>
   <si>
@@ -2792,12 +2492,6 @@
     <t>https://adserver.doctoreto.com/www/images/a2948c653558a2250afc92de749f8cd0.webp</t>
   </si>
   <si>
-    <t>1404/07/09</t>
-  </si>
-  <si>
-    <t>1404/10/09</t>
-  </si>
-  <si>
     <t>Dr. Jafari</t>
   </si>
   <si>
@@ -2807,12 +2501,6 @@
     <t>https://adserver.doctoreto.com/www/images/0800d8be3d8db30885f7d624f521892a.jpg</t>
   </si>
   <si>
-    <t>1404/02/30</t>
-  </si>
-  <si>
-    <t>1404/05/30</t>
-  </si>
-  <si>
     <t>Dr. Moghadam</t>
   </si>
   <si>
@@ -2822,12 +2510,6 @@
     <t>https://adserver.doctoreto.com/www/images/00ea4294f5782de03ca1c4774ec5b428.webp</t>
   </si>
   <si>
-    <t>1404/08/24</t>
-  </si>
-  <si>
-    <t>1404/11/24</t>
-  </si>
-  <si>
     <t>Dr. Mohsen Dadashi</t>
   </si>
   <si>
@@ -2852,12 +2534,6 @@
     <t>https://adserver.doctoreto.com/www/images/a97fec6f81f2f4dd49bdd9b434911d5e.webp</t>
   </si>
   <si>
-    <t>1404/09/18</t>
-  </si>
-  <si>
-    <t>1404/12/18</t>
-  </si>
-  <si>
     <t>Dr. Naghme Avari 02</t>
   </si>
   <si>
@@ -2885,12 +2561,6 @@
     <t>https://adserver.doctoreto.com/www/images/b81a3fcb7e9a9e57d094ce2634956ae2.webp</t>
   </si>
   <si>
-    <t>1404/09/17</t>
-  </si>
-  <si>
-    <t>1404/12/17</t>
-  </si>
-  <si>
     <t>DR. Tajali</t>
   </si>
   <si>
@@ -2903,12 +2573,6 @@
     <t>https://adserver.doctoreto.com/www/images/845ea3e2a478215e606a15d79e891849.webp</t>
   </si>
   <si>
-    <t>1404/05/21</t>
-  </si>
-  <si>
-    <t>1404/08/21</t>
-  </si>
-  <si>
     <t>Dr. Yazdan Panah</t>
   </si>
   <si>
@@ -2918,12 +2582,6 @@
     <t>https://adserver.doctoreto.com/www/images/22fb61e69e8c050ad385458804cf7dfd.webp</t>
   </si>
   <si>
-    <t>1404/08/28</t>
-  </si>
-  <si>
-    <t>1404/11/28</t>
-  </si>
-  <si>
     <t>DR. Zahra Kiani</t>
   </si>
   <si>
@@ -2945,12 +2603,6 @@
     <t>https://adserver.doctoreto.com/www/images/f6f5418365fd70c8b107315b02a5f3b2.webp</t>
   </si>
   <si>
-    <t>1404/10/10</t>
-  </si>
-  <si>
-    <t>1405/01/10</t>
-  </si>
-  <si>
     <t>Markaz-e Jame urology Dr Ghazi</t>
   </si>
   <si>
@@ -2963,12 +2615,6 @@
     <t>https://adserver.doctoreto.com/www/images/aeadcbb7bb1a71cf180d91411c10a71b.webp</t>
   </si>
   <si>
-    <t>1404/01/30</t>
-  </si>
-  <si>
-    <t>1404/04/30</t>
-  </si>
-  <si>
     <t>NDK Mind Clinic</t>
   </si>
   <si>
@@ -2991,6 +2637,87 @@
   </si>
   <si>
     <t>Nastaran</t>
+  </si>
+  <si>
+    <t>1405/04/06</t>
+  </si>
+  <si>
+    <t>1405/05/24</t>
+  </si>
+  <si>
+    <t>1405/08/24</t>
+  </si>
+  <si>
+    <t>1405/08/26</t>
+  </si>
+  <si>
+    <t>1405/03/15</t>
+  </si>
+  <si>
+    <t>1405/06/15</t>
+  </si>
+  <si>
+    <t>1405/05/16</t>
+  </si>
+  <si>
+    <t>1405/09/16</t>
+  </si>
+  <si>
+    <t>1405/09/11</t>
+  </si>
+  <si>
+    <t>1405/05/25</t>
+  </si>
+  <si>
+    <t>1405/08/25</t>
+  </si>
+  <si>
+    <t>shahrzad</t>
+  </si>
+  <si>
+    <t>1405/06/25</t>
+  </si>
+  <si>
+    <t>1405/04/04</t>
+  </si>
+  <si>
+    <t>1405/07/04</t>
+  </si>
+  <si>
+    <t>1405/02/30</t>
+  </si>
+  <si>
+    <t>1405/02/16</t>
+  </si>
+  <si>
+    <t>1405/05/28</t>
+  </si>
+  <si>
+    <t>1405/08/28</t>
+  </si>
+  <si>
+    <t>1405/09/03</t>
+  </si>
+  <si>
+    <t>1405/04/17</t>
+  </si>
+  <si>
+    <t>1405/07/17</t>
+  </si>
+  <si>
+    <t>1405/06/14</t>
+  </si>
+  <si>
+    <t>1405/09/14</t>
+  </si>
+  <si>
+    <t>1405/07/26</t>
+  </si>
+  <si>
+    <t>1405/04/07</t>
+  </si>
+  <si>
+    <t>1405/07/07</t>
   </si>
 </sst>
 </file>
@@ -3439,798 +3166,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Sheet1"/>
-      <sheetName val="Sheet2"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="A1" t="str">
-            <v>Campaign Name</v>
-          </cell>
-          <cell r="B1" t="str">
-            <v>Account Manager</v>
-          </cell>
-          <cell r="C1" t="str">
-            <v>Start Date</v>
-          </cell>
-          <cell r="D1" t="str">
-            <v>End Date</v>
-          </cell>
-          <cell r="E1" t="str">
-            <v>Price</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="A2" t="str">
-            <v>Dr Amir Azizi</v>
-          </cell>
-          <cell r="B2" t="str">
-            <v>Sanam</v>
-          </cell>
-          <cell r="C2" t="str">
-            <v>1405/04/06</v>
-          </cell>
-          <cell r="D2" t="str">
-            <v>1405/07/06</v>
-          </cell>
-          <cell r="E2">
-            <v>30600000</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="A3" t="str">
-            <v>DR Ali Saeedi</v>
-          </cell>
-          <cell r="B3" t="str">
-            <v>shahrzad</v>
-          </cell>
-          <cell r="C3" t="str">
-            <v>1405/03/26</v>
-          </cell>
-          <cell r="D3" t="str">
-            <v>1405/06/25</v>
-          </cell>
-          <cell r="E3">
-            <v>55000000</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="A4" t="str">
-            <v>DR Ali NaserBakhT</v>
-          </cell>
-          <cell r="B4" t="str">
-            <v>elahe</v>
-          </cell>
-          <cell r="C4" t="str">
-            <v>1405/02/29</v>
-          </cell>
-          <cell r="D4" t="str">
-            <v>1405/05/29</v>
-          </cell>
-          <cell r="E4">
-            <v>132000000</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="A5" t="str">
-            <v>Dr AssaEi</v>
-          </cell>
-          <cell r="B5" t="str">
-            <v>Nastaran</v>
-          </cell>
-          <cell r="C5" t="str">
-            <v>1405/05/26</v>
-          </cell>
-          <cell r="D5" t="str">
-            <v>1405/08/26</v>
-          </cell>
-          <cell r="E5">
-            <v>20000000</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="A6" t="str">
-            <v>DR Azadeh Khalajian</v>
-          </cell>
-          <cell r="B6" t="str">
-            <v>Sanam</v>
-          </cell>
-          <cell r="C6" t="str">
-            <v>1405/03/15</v>
-          </cell>
-          <cell r="D6" t="str">
-            <v>1405/06/15</v>
-          </cell>
-          <cell r="E6">
-            <v>60000000</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="A7" t="str">
-            <v>Dr Atefe Faramarzi</v>
-          </cell>
-          <cell r="B7" t="str">
-            <v>Naser</v>
-          </cell>
-          <cell r="C7" t="str">
-            <v>1405/05/05</v>
-          </cell>
-          <cell r="D7" t="str">
-            <v>1405/08/05</v>
-          </cell>
-          <cell r="E7">
-            <v>135000000</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="A8" t="str">
-            <v>DR Ata Heydari</v>
-          </cell>
-          <cell r="B8" t="str">
-            <v>Naser</v>
-          </cell>
-          <cell r="E8">
-            <v>150000000</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="A9" t="str">
-            <v>Dr Azhie</v>
-          </cell>
-          <cell r="B9" t="str">
-            <v>Naser</v>
-          </cell>
-          <cell r="C9" t="str">
-            <v>1405/05/19</v>
-          </cell>
-          <cell r="D9" t="str">
-            <v>1405/08/19</v>
-          </cell>
-          <cell r="E9">
-            <v>140000000</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="A10" t="str">
-            <v>Dr Azadeh MirMaasoumi</v>
-          </cell>
-          <cell r="B10" t="str">
-            <v>Sara</v>
-          </cell>
-          <cell r="C10" t="str">
-            <v>1405/03/16</v>
-          </cell>
-          <cell r="D10" t="str">
-            <v>1405/05/16</v>
-          </cell>
-          <cell r="E10">
-            <v>45000000</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="A11" t="str">
-            <v>Dr Homa Sharifi</v>
-          </cell>
-          <cell r="B11" t="str">
-            <v>Sara</v>
-          </cell>
-          <cell r="C11" t="str">
-            <v>1405/04/08</v>
-          </cell>
-          <cell r="D11" t="str">
-            <v>1405/07/08</v>
-          </cell>
-          <cell r="E11">
-            <v>27000000</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="A12" t="str">
-            <v>Dr Zarin BadiNi</v>
-          </cell>
-          <cell r="B12" t="str">
-            <v>Sanam</v>
-          </cell>
-          <cell r="C12" t="str">
-            <v>1405/04/29</v>
-          </cell>
-          <cell r="D12" t="str">
-            <v>1405/07/29</v>
-          </cell>
-          <cell r="E12">
-            <v>240000000</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="A13" t="str">
-            <v>DR Zeynab Tavana</v>
-          </cell>
-          <cell r="B13" t="str">
-            <v>Nastaran</v>
-          </cell>
-          <cell r="C13" t="str">
-            <v>1405/05/19</v>
-          </cell>
-          <cell r="D13" t="str">
-            <v>1405/08/19</v>
-          </cell>
-          <cell r="E13">
-            <v>8800000</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="A14" t="str">
-            <v>Dr. Farshad Sadeghi</v>
-          </cell>
-          <cell r="B14" t="str">
-            <v>Sara</v>
-          </cell>
-          <cell r="C14" t="str">
-            <v>1405/04/10</v>
-          </cell>
-          <cell r="D14" t="str">
-            <v>1405/07/10</v>
-          </cell>
-          <cell r="E14">
-            <v>60000000</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="A15" t="str">
-            <v>Dr. Amir Bastani</v>
-          </cell>
-          <cell r="B15" t="str">
-            <v>Nastaran</v>
-          </cell>
-          <cell r="C15" t="str">
-            <v>1405/03/09</v>
-          </cell>
-          <cell r="D15" t="str">
-            <v>1405/06/09</v>
-          </cell>
-          <cell r="E15">
-            <v>36000000</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="A16" t="str">
-            <v>Dr. Ghazi</v>
-          </cell>
-          <cell r="B16" t="str">
-            <v>Naser</v>
-          </cell>
-          <cell r="C16" t="str">
-            <v>1405/06/04</v>
-          </cell>
-          <cell r="D16" t="str">
-            <v>1405/09/04</v>
-          </cell>
-          <cell r="E16">
-            <v>427000000</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="A17" t="str">
-            <v>Dr. Hadi Mansouri</v>
-          </cell>
-          <cell r="B17" t="str">
-            <v>Nastaran</v>
-          </cell>
-          <cell r="C17" t="str">
-            <v>1405/04/02</v>
-          </cell>
-          <cell r="D17" t="str">
-            <v>1405/07/02</v>
-          </cell>
-          <cell r="E17">
-            <v>46200000</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="A18" t="str">
-            <v>Dr. Izadpanah</v>
-          </cell>
-          <cell r="B18" t="str">
-            <v>Sara</v>
-          </cell>
-          <cell r="C18" t="str">
-            <v>1405/04/28</v>
-          </cell>
-          <cell r="D18" t="str">
-            <v>1405/07/28</v>
-          </cell>
-          <cell r="E18">
-            <v>75000000</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="A19" t="str">
-            <v>Dr. Hengame Mehrfar</v>
-          </cell>
-          <cell r="B19" t="str">
-            <v>shahrzad</v>
-          </cell>
-          <cell r="C19" t="str">
-            <v>1405/05/25</v>
-          </cell>
-          <cell r="D19" t="str">
-            <v>1405/08/25</v>
-          </cell>
-          <cell r="E19">
-            <v>46200000</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="A20" t="str">
-            <v>Dr. Mohammad Borzoyi</v>
-          </cell>
-          <cell r="B20" t="str">
-            <v>shahrzad</v>
-          </cell>
-          <cell r="C20" t="str">
-            <v>1405/03/04</v>
-          </cell>
-          <cell r="D20" t="str">
-            <v>1405/06/04</v>
-          </cell>
-          <cell r="E20">
-            <v>49500000</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="A21" t="str">
-            <v>Dr. Mayryam Farokhshahi</v>
-          </cell>
-          <cell r="B21" t="str">
-            <v>shahrzad</v>
-          </cell>
-          <cell r="C21" t="str">
-            <v>1405/06/02</v>
-          </cell>
-          <cell r="D21" t="str">
-            <v>1405/09/02</v>
-          </cell>
-          <cell r="E21">
-            <v>6600000</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="A22" t="str">
-            <v>Dr. Kartalayi</v>
-          </cell>
-          <cell r="B22" t="str">
-            <v>shahrzad</v>
-          </cell>
-          <cell r="C22" t="str">
-            <v>1405/05/29</v>
-          </cell>
-          <cell r="D22" t="str">
-            <v>1405/08/29</v>
-          </cell>
-          <cell r="E22">
-            <v>41580000</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="A23" t="str">
-            <v>Dr. Negin Asna Asahari</v>
-          </cell>
-          <cell r="B23" t="str">
-            <v>Nastaran</v>
-          </cell>
-          <cell r="C23" t="str">
-            <v>1405/06/16</v>
-          </cell>
-          <cell r="D23" t="str">
-            <v>1405/09/16</v>
-          </cell>
-          <cell r="E23">
-            <v>23100000</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="A24" t="str">
-            <v>Dr. Natami</v>
-          </cell>
-          <cell r="B24" t="str">
-            <v>Nastaran</v>
-          </cell>
-          <cell r="C24" t="str">
-            <v>1405/03/25</v>
-          </cell>
-          <cell r="D24" t="str">
-            <v>1405/06/25</v>
-          </cell>
-          <cell r="E24">
-            <v>33000000</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="A25" t="str">
-            <v>Dr. YazdanShenas</v>
-          </cell>
-          <cell r="B25" t="str">
-            <v>Nastaran</v>
-          </cell>
-          <cell r="C25" t="str">
-            <v>1405/03/17</v>
-          </cell>
-          <cell r="D25" t="str">
-            <v>1405/06/17</v>
-          </cell>
-          <cell r="E25">
-            <v>170000000</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="A26" t="str">
-            <v>Dr. Sahar Tavakoli</v>
-          </cell>
-          <cell r="B26" t="str">
-            <v>shahrzad</v>
-          </cell>
-          <cell r="C26" t="str">
-            <v>1405/06/16</v>
-          </cell>
-          <cell r="D26" t="str">
-            <v>1405/09/16</v>
-          </cell>
-          <cell r="E26">
-            <v>30000000</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="A27" t="str">
-            <v>Farzin Khorvash</v>
-          </cell>
-          <cell r="B27" t="str">
-            <v>Nastaran</v>
-          </cell>
-          <cell r="C27" t="str">
-            <v>1405/04/04</v>
-          </cell>
-          <cell r="D27" t="str">
-            <v>1405/07/04</v>
-          </cell>
-          <cell r="E27">
-            <v>49500000</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="A28" t="str">
-            <v>Farzane Mortazavi Far</v>
-          </cell>
-          <cell r="B28" t="str">
-            <v>Nastaran</v>
-          </cell>
-          <cell r="C28" t="str">
-            <v>1405/04/27</v>
-          </cell>
-          <cell r="D28" t="str">
-            <v>1405/07/27</v>
-          </cell>
-          <cell r="E28">
-            <v>72600000</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="A29" t="str">
-            <v>Farnaz Bagherian</v>
-          </cell>
-          <cell r="B29" t="str">
-            <v>Nastaran</v>
-          </cell>
-          <cell r="C29" t="str">
-            <v>1405/05/24</v>
-          </cell>
-          <cell r="D29" t="str">
-            <v>1405/08/24</v>
-          </cell>
-          <cell r="E29">
-            <v>6600000</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="A30" t="str">
-            <v>Hamed Mahmoudi</v>
-          </cell>
-          <cell r="B30" t="str">
-            <v>Naser</v>
-          </cell>
-          <cell r="C30" t="str">
-            <v>1405/05/06</v>
-          </cell>
-          <cell r="D30" t="str">
-            <v>1405/08/06</v>
-          </cell>
-          <cell r="E30">
-            <v>206000000</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="A31" t="str">
-            <v>Fateme Golestani</v>
-          </cell>
-          <cell r="B31" t="str">
-            <v>Sara</v>
-          </cell>
-          <cell r="C31" t="str">
-            <v>1405/03/30</v>
-          </cell>
-          <cell r="D31" t="str">
-            <v>1405/06/30</v>
-          </cell>
-          <cell r="E31">
-            <v>34000000</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="A32" t="str">
-            <v>HamidReza Ziayie</v>
-          </cell>
-          <cell r="B32" t="str">
-            <v>Nastaran</v>
-          </cell>
-          <cell r="C32" t="str">
-            <v>1405/03/18</v>
-          </cell>
-          <cell r="D32" t="str">
-            <v>1405/06/18</v>
-          </cell>
-          <cell r="E32">
-            <v>76000000</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="A33" t="str">
-            <v>Hamid MehraBi</v>
-          </cell>
-          <cell r="B33" t="str">
-            <v>Mohamad</v>
-          </cell>
-          <cell r="C33" t="str">
-            <v>1405/04/16</v>
-          </cell>
-          <cell r="D33" t="str">
-            <v>1405/07/16</v>
-          </cell>
-          <cell r="E33">
-            <v>60000000</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="A34" t="str">
-            <v>HonarVAr</v>
-          </cell>
-          <cell r="B34" t="str">
-            <v>Nastaran</v>
-          </cell>
-          <cell r="C34" t="str">
-            <v>1405/02/30</v>
-          </cell>
-          <cell r="D34" t="str">
-            <v>1405/05/30</v>
-          </cell>
-          <cell r="E34">
-            <v>39600000</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="A35" t="str">
-            <v>Hashem Rafie Zadeh</v>
-          </cell>
-          <cell r="B35" t="str">
-            <v>Mohamad</v>
-          </cell>
-          <cell r="C35" t="str">
-            <v>1405/04/20</v>
-          </cell>
-          <cell r="D35" t="str">
-            <v>1405/07/20</v>
-          </cell>
-          <cell r="E35">
-            <v>42900000</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="A36" t="str">
-            <v>Keyvan Rezaie</v>
-          </cell>
-          <cell r="B36" t="str">
-            <v>Naser</v>
-          </cell>
-          <cell r="C36" t="str">
-            <v>1405/05/26</v>
-          </cell>
-          <cell r="D36" t="str">
-            <v>1405/08/26</v>
-          </cell>
-          <cell r="E36">
-            <v>99000000</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="A37" t="str">
-            <v>Khashayar KhaniZadeh</v>
-          </cell>
-          <cell r="B37" t="str">
-            <v>Naser</v>
-          </cell>
-          <cell r="C37" t="str">
-            <v>1405/05/11</v>
-          </cell>
-          <cell r="D37" t="str">
-            <v>1405/08/11</v>
-          </cell>
-          <cell r="E37">
-            <v>44000000</v>
-          </cell>
-        </row>
-        <row r="38">
-          <cell r="A38" t="str">
-            <v>Lale Izadi</v>
-          </cell>
-          <cell r="B38" t="str">
-            <v>Sanam</v>
-          </cell>
-          <cell r="C38" t="str">
-            <v>1405/05/06</v>
-          </cell>
-          <cell r="D38" t="str">
-            <v>1405/08/06</v>
-          </cell>
-          <cell r="E38">
-            <v>80000000</v>
-          </cell>
-        </row>
-        <row r="39">
-          <cell r="A39" t="str">
-            <v>KIMIA Ghasemi</v>
-          </cell>
-          <cell r="B39" t="str">
-            <v>Mohamad</v>
-          </cell>
-          <cell r="C39" t="str">
-            <v>1405/05/03</v>
-          </cell>
-          <cell r="D39" t="str">
-            <v>1405/08/03</v>
-          </cell>
-          <cell r="E39">
-            <v>29700000</v>
-          </cell>
-        </row>
-        <row r="40">
-          <cell r="A40" t="str">
-            <v>Khatereh Jafari</v>
-          </cell>
-          <cell r="B40" t="str">
-            <v>Sanam</v>
-          </cell>
-          <cell r="C40" t="str">
-            <v>1405/04/08</v>
-          </cell>
-          <cell r="D40" t="str">
-            <v>1405/07/08</v>
-          </cell>
-          <cell r="E40">
-            <v>30000000</v>
-          </cell>
-        </row>
-        <row r="41">
-          <cell r="A41" t="str">
-            <v>Mansoureh AmirShahi</v>
-          </cell>
-          <cell r="B41" t="str">
-            <v>Nastaran</v>
-          </cell>
-          <cell r="C41" t="str">
-            <v>1405/06/16</v>
-          </cell>
-          <cell r="D41" t="str">
-            <v>1405/09/16</v>
-          </cell>
-          <cell r="E41">
-            <v>33000000</v>
-          </cell>
-        </row>
-        <row r="42">
-          <cell r="A42" t="str">
-            <v>Maasoume Zare</v>
-          </cell>
-          <cell r="B42" t="str">
-            <v>Shaqayeq</v>
-          </cell>
-          <cell r="C42" t="str">
-            <v>1405/04/28</v>
-          </cell>
-          <cell r="D42" t="str">
-            <v>1405/07/28</v>
-          </cell>
-          <cell r="E42">
-            <v>30000000</v>
-          </cell>
-        </row>
-        <row r="43">
-          <cell r="A43" t="str">
-            <v>Maryam Gholami</v>
-          </cell>
-          <cell r="B43" t="str">
-            <v>Mohamad</v>
-          </cell>
-          <cell r="C43" t="str">
-            <v>1405/02/16</v>
-          </cell>
-          <cell r="D43" t="str">
-            <v>1405/05/16</v>
-          </cell>
-          <cell r="E43">
-            <v>46200000</v>
-          </cell>
-        </row>
-        <row r="44">
-          <cell r="A44" t="str">
-            <v>Maryam DadKhah</v>
-          </cell>
-          <cell r="B44" t="str">
-            <v>Sanam</v>
-          </cell>
-          <cell r="C44" t="str">
-            <v>1405/05/27</v>
-          </cell>
-          <cell r="D44" t="str">
-            <v>1405/08/27</v>
-          </cell>
-          <cell r="E44">
-            <v>40000000</v>
-          </cell>
-        </row>
-        <row r="45">
-          <cell r="A45" t="str">
-            <v>Meysam Ghanbari</v>
-          </cell>
-          <cell r="B45" t="str">
-            <v>shahrzad</v>
-          </cell>
-          <cell r="C45" t="str">
-            <v>1405/05/28</v>
-          </cell>
-          <cell r="D45" t="str">
-            <v>1405/08/28</v>
-          </cell>
-          <cell r="E45">
-            <v>82500000</v>
-          </cell>
-        </row>
-        <row r="46">
-          <cell r="A46" t="str">
-            <v>Mazaher Hadi</v>
-          </cell>
-          <cell r="B46" t="str">
-            <v>shahrzad</v>
-          </cell>
-          <cell r="C46" t="str">
-            <v>1405/05/10</v>
-          </cell>
-          <cell r="D46" t="str">
-            <v>1405/08/10</v>
-          </cell>
-          <cell r="E46">
-            <v>58000000</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -5194,7 +4129,7 @@
         <v>142</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>983</v>
+        <v>865</v>
       </c>
       <c r="H25" s="12">
         <v>45000000</v>
@@ -5355,7 +4290,6 @@
         <v>26</v>
       </c>
       <c r="H32" s="12">
-        <f>VLOOKUP(A32,[1]Sheet2!A:E,5,0)</f>
         <v>132000000</v>
       </c>
     </row>
@@ -5382,7 +4316,6 @@
         <v>26</v>
       </c>
       <c r="H33" s="12">
-        <f>VLOOKUP(A33,[1]Sheet2!A:E,5,0)</f>
         <v>132000000</v>
       </c>
     </row>
@@ -5409,7 +4342,6 @@
         <v>13</v>
       </c>
       <c r="H34" s="12">
-        <f>VLOOKUP(A34,[1]Sheet2!A:E,5,0)</f>
         <v>55000000</v>
       </c>
     </row>
@@ -5427,17 +4359,15 @@
         <v>191</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>192</v>
+        <v>866</v>
       </c>
       <c r="F35" s="25" t="s">
         <v>193</v>
       </c>
-      <c r="G35" s="1" t="str">
-        <f>VLOOKUP(A35,[1]Sheet2!A:B,2,0)</f>
-        <v>Sanam</v>
+      <c r="G35" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="H35" s="12">
-        <f>VLOOKUP(A35,[1]Sheet2!A:E,5,0)</f>
         <v>30600000</v>
       </c>
     </row>
@@ -5455,13 +4385,17 @@
         <v>197</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>198</v>
+        <v>867</v>
       </c>
       <c r="F36" s="26" t="s">
-        <v>199</v>
-      </c>
-      <c r="G36" s="1"/>
-      <c r="H36" s="12"/>
+        <v>868</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>865</v>
+      </c>
+      <c r="H36" s="12">
+        <v>6600000</v>
+      </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
@@ -5477,17 +4411,15 @@
         <v>203</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>204</v>
+        <v>543</v>
       </c>
       <c r="F37" s="26" t="s">
-        <v>199</v>
-      </c>
-      <c r="G37" s="1" t="str">
-        <f>VLOOKUP(A37,[1]Sheet2!A:B,2,0)</f>
-        <v>Nastaran</v>
+        <v>869</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>865</v>
       </c>
       <c r="H37" s="12">
-        <f>VLOOKUP(A37,[1]Sheet2!A:E,5,0)</f>
         <v>20000000</v>
       </c>
     </row>
@@ -5504,167 +4436,161 @@
       <c r="D38" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="E38" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="F38" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="G38" s="1" t="str">
-        <f>VLOOKUP(A38,[1]Sheet2!A:B,2,0)</f>
-        <v>Naser</v>
+      <c r="E38" s="1">
+        <v>0</v>
+      </c>
+      <c r="F38" s="6">
+        <v>0</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="H38" s="12">
-        <f>VLOOKUP(A38,[1]Sheet2!A:E,5,0)</f>
         <v>150000000</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C39" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="D39" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="C39" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>214</v>
-      </c>
       <c r="E39" s="1" t="s">
-        <v>215</v>
+        <v>294</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="G39" s="1" t="str">
-        <f>VLOOKUP(A39,[1]Sheet2!A:B,2,0)</f>
-        <v>Naser</v>
+        <v>295</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="H39" s="12">
-        <f>VLOOKUP(A39,[1]Sheet2!A:E,5,0)</f>
         <v>135000000</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C40" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="D40" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="C40" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>220</v>
-      </c>
       <c r="E40" s="1" t="s">
-        <v>221</v>
+        <v>870</v>
       </c>
       <c r="F40" s="27" t="s">
-        <v>222</v>
-      </c>
-      <c r="G40" s="1" t="str">
-        <f>VLOOKUP(A40,[1]Sheet2!A:B,2,0)</f>
-        <v>Sanam</v>
+        <v>871</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="H40" s="12">
-        <f>VLOOKUP(A40,[1]Sheet2!A:E,5,0)</f>
         <v>60000000</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>192</v>
+        <v>288</v>
       </c>
       <c r="F41" s="25" t="s">
-        <v>193</v>
-      </c>
-      <c r="G41" s="1" t="str">
-        <f>VLOOKUP(A41,[1]Sheet2!A:B,2,0)</f>
-        <v>Sara</v>
+        <v>872</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="H41" s="12">
-        <f>VLOOKUP(A41,[1]Sheet2!A:E,5,0)</f>
         <v>45000000</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>71</v>
+        <v>328</v>
       </c>
       <c r="F42" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="G42" s="1" t="str">
-        <f>VLOOKUP(A42,[1]Sheet2!A:B,2,0)</f>
-        <v>Naser</v>
+        <v>329</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="H42" s="12">
-        <f>VLOOKUP(A42,[1]Sheet2!A:E,5,0)</f>
         <v>140000000</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>234</v>
+        <v>93</v>
       </c>
       <c r="F43" s="6" t="s">
-        <v>235</v>
-      </c>
-      <c r="G43" s="1"/>
-      <c r="H43" s="12"/>
+        <v>94</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H43" s="12">
+        <v>11000000</v>
+      </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>112</v>
@@ -5672,357 +4598,375 @@
       <c r="F44" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="G44" s="1"/>
-      <c r="H44" s="12"/>
+      <c r="G44" s="1" t="s">
+        <v>865</v>
+      </c>
+      <c r="H44" s="12">
+        <v>18700000</v>
+      </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="F45" s="6" t="s">
-        <v>244</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="E45" s="1"/>
+      <c r="F45" s="6"/>
       <c r="G45" s="1"/>
       <c r="H45" s="12"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>248</v>
+        <v>192</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="G46" s="1" t="str">
-        <f>VLOOKUP(A46,[1]Sheet2!A:B,2,0)</f>
-        <v>Sara</v>
+        <v>193</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="H46" s="12">
-        <f>VLOOKUP(A46,[1]Sheet2!A:E,5,0)</f>
         <v>27000000</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="F47" s="28" t="s">
-        <v>255</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="E47" s="1"/>
+      <c r="F47" s="28"/>
       <c r="G47" s="1"/>
       <c r="H47" s="12"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>65</v>
+        <v>437</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>260</v>
-      </c>
-      <c r="G48" s="1"/>
-      <c r="H48" s="12"/>
+        <v>60</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H48" s="12">
+        <v>50000000</v>
+      </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>221</v>
+        <v>461</v>
       </c>
       <c r="F49" s="27" t="s">
-        <v>222</v>
-      </c>
-      <c r="G49" s="1"/>
-      <c r="H49" s="12"/>
+        <v>462</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H49" s="12">
+        <v>140000000</v>
+      </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>221</v>
+        <v>461</v>
       </c>
       <c r="F50" s="27" t="s">
-        <v>222</v>
-      </c>
-      <c r="G50" s="1"/>
-      <c r="H50" s="12"/>
+        <v>462</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H50" s="12">
+        <v>140000000</v>
+      </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="F51" s="29" t="s">
         <v>268</v>
       </c>
-      <c r="B51" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="F51" s="29" t="s">
-        <v>273</v>
-      </c>
-      <c r="G51" s="1"/>
-      <c r="H51" s="12"/>
+      <c r="G51" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H51" s="12">
+        <v>100000000</v>
+      </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="F52" s="30" t="s">
-        <v>279</v>
-      </c>
-      <c r="G52" s="1"/>
-      <c r="H52" s="12"/>
+        <v>873</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H52" s="12">
+        <v>165000000</v>
+      </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>280</v>
+        <v>269</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="F53" s="6" t="s">
-        <v>285</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="E53" s="1"/>
+      <c r="F53" s="6"/>
       <c r="G53" s="1"/>
       <c r="H53" s="12"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>286</v>
+        <v>273</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>286</v>
+        <v>273</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F54" s="31" t="s">
-        <v>40</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="E54" s="1"/>
+      <c r="F54" s="31"/>
       <c r="G54" s="1"/>
       <c r="H54" s="12"/>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>289</v>
+        <v>276</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>290</v>
+        <v>277</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>291</v>
+        <v>278</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>292</v>
+        <v>279</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>293</v>
+        <v>737</v>
       </c>
       <c r="F55" s="6" t="s">
-        <v>294</v>
-      </c>
-      <c r="G55" s="1"/>
-      <c r="H55" s="12"/>
+        <v>738</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H55" s="12">
+        <v>99000000</v>
+      </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>295</v>
+        <v>280</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>296</v>
+        <v>281</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>297</v>
+        <v>282</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="F56" s="22" t="s">
-        <v>175</v>
-      </c>
+        <v>283</v>
+      </c>
+      <c r="E56" s="1"/>
+      <c r="F56" s="22"/>
       <c r="G56" s="1"/>
       <c r="H56" s="12"/>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>299</v>
+        <v>284</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>300</v>
+        <v>285</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>301</v>
+        <v>286</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>302</v>
+        <v>287</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>303</v>
+        <v>461</v>
       </c>
       <c r="F57" s="32" t="s">
-        <v>304</v>
-      </c>
-      <c r="G57" s="1"/>
-      <c r="H57" s="12"/>
+        <v>462</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>865</v>
+      </c>
+      <c r="H57" s="12">
+        <v>350000000</v>
+      </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>306</v>
+        <v>291</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>308</v>
+        <v>293</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>309</v>
+        <v>174</v>
       </c>
       <c r="F58" s="33" t="s">
-        <v>310</v>
-      </c>
-      <c r="G58" s="1"/>
-      <c r="H58" s="12"/>
+        <v>175</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H58" s="12">
+        <v>70000000</v>
+      </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>311</v>
+        <v>296</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>312</v>
+        <v>297</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>313</v>
+        <v>298</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>314</v>
+        <v>299</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>278</v>
+        <v>742</v>
       </c>
       <c r="F59" s="30" t="s">
-        <v>279</v>
-      </c>
-      <c r="G59" s="1"/>
-      <c r="H59" s="12"/>
+        <v>874</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H59" s="12">
+        <v>36300000</v>
+      </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>315</v>
+        <v>300</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>315</v>
+        <v>300</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>316</v>
+        <v>301</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>317</v>
+        <v>302</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>204</v>
@@ -6030,484 +4974,467 @@
       <c r="F60" s="26" t="s">
         <v>199</v>
       </c>
-      <c r="G60" s="1"/>
-      <c r="H60" s="12"/>
+      <c r="G60" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H60" s="12">
+        <v>33000000</v>
+      </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>318</v>
+        <v>303</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>318</v>
+        <v>303</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>319</v>
+        <v>304</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>320</v>
+        <v>305</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>93</v>
+        <v>213</v>
       </c>
       <c r="F61" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="G61" s="1"/>
-      <c r="H61" s="12"/>
+        <v>214</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H61" s="12">
+        <v>76000000</v>
+      </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>321</v>
+        <v>306</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>322</v>
+        <v>307</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>323</v>
+        <v>308</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>324</v>
+        <v>309</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>325</v>
+        <v>452</v>
       </c>
       <c r="F62" s="34" t="s">
-        <v>326</v>
-      </c>
-      <c r="G62" s="1" t="str">
-        <f>VLOOKUP(A62,[1]Sheet2!A:B,2,0)</f>
-        <v>Sanam</v>
+        <v>453</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="H62" s="12">
-        <f>VLOOKUP(A62,[1]Sheet2!A:E,5,0)</f>
         <v>240000000</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>321</v>
+        <v>306</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>327</v>
+        <v>312</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>328</v>
+        <v>313</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>329</v>
+        <v>314</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>325</v>
+        <v>452</v>
       </c>
       <c r="F63" s="34" t="s">
-        <v>326</v>
-      </c>
-      <c r="G63" s="1" t="str">
-        <f>VLOOKUP(A63,[1]Sheet2!A:B,2,0)</f>
-        <v>Sanam</v>
+        <v>453</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="H63" s="12">
-        <f>VLOOKUP(A63,[1]Sheet2!A:E,5,0)</f>
         <v>240000000</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>321</v>
+        <v>306</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>330</v>
+        <v>315</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>331</v>
+        <v>316</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>332</v>
+        <v>317</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>325</v>
+        <v>452</v>
       </c>
       <c r="F64" s="34" t="s">
-        <v>326</v>
-      </c>
-      <c r="G64" s="1" t="str">
-        <f>VLOOKUP(A64,[1]Sheet2!A:B,2,0)</f>
-        <v>Sanam</v>
+        <v>453</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="H64" s="12">
-        <f>VLOOKUP(A64,[1]Sheet2!A:E,5,0)</f>
         <v>240000000</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>321</v>
+        <v>306</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>333</v>
+        <v>318</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>334</v>
+        <v>319</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>335</v>
+        <v>320</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>325</v>
+        <v>452</v>
       </c>
       <c r="F65" s="34" t="s">
-        <v>326</v>
-      </c>
-      <c r="G65" s="1" t="str">
-        <f>VLOOKUP(A65,[1]Sheet2!A:B,2,0)</f>
-        <v>Sanam</v>
+        <v>453</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="H65" s="12">
-        <f>VLOOKUP(A65,[1]Sheet2!A:E,5,0)</f>
         <v>240000000</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B66" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="B66" s="1" t="s">
-        <v>336</v>
-      </c>
       <c r="C66" s="1" t="s">
-        <v>337</v>
+        <v>322</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>338</v>
+        <v>323</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>325</v>
+        <v>452</v>
       </c>
       <c r="F66" s="34" t="s">
-        <v>326</v>
-      </c>
-      <c r="G66" s="1" t="str">
-        <f>VLOOKUP(A66,[1]Sheet2!A:B,2,0)</f>
-        <v>Sanam</v>
+        <v>453</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="H66" s="12">
-        <f>VLOOKUP(A66,[1]Sheet2!A:E,5,0)</f>
         <v>240000000</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>339</v>
+        <v>324</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>340</v>
+        <v>325</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>341</v>
+        <v>326</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>342</v>
+        <v>327</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>343</v>
+        <v>328</v>
       </c>
       <c r="F67" s="35" t="s">
-        <v>344</v>
-      </c>
-      <c r="G67" s="1" t="str">
-        <f>VLOOKUP(A67,[1]Sheet2!A:B,2,0)</f>
-        <v>Nastaran</v>
+        <v>329</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>865</v>
       </c>
       <c r="H67" s="12">
-        <f>VLOOKUP(A67,[1]Sheet2!A:E,5,0)</f>
         <v>8800000</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>345</v>
+        <v>330</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>345</v>
+        <v>330</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>346</v>
+        <v>331</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>347</v>
+        <v>332</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>348</v>
+        <v>70</v>
       </c>
       <c r="F68" s="6" t="s">
-        <v>349</v>
-      </c>
-      <c r="G68" s="1" t="str">
-        <f>VLOOKUP(A68,[1]Sheet2!A:B,2,0)</f>
-        <v>Nastaran</v>
+        <v>71</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>865</v>
       </c>
       <c r="H68" s="12">
-        <f>VLOOKUP(A68,[1]Sheet2!A:E,5,0)</f>
         <v>36000000</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>350</v>
+        <v>333</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>351</v>
+        <v>334</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>352</v>
+        <v>335</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>353</v>
+        <v>336</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>354</v>
+        <v>123</v>
       </c>
       <c r="F69" s="6" t="s">
-        <v>355</v>
-      </c>
-      <c r="G69" s="1"/>
-      <c r="H69" s="12"/>
+        <v>124</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H69" s="12">
+        <v>60000000</v>
+      </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>356</v>
+        <v>337</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>357</v>
+        <v>338</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>358</v>
+        <v>339</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>359</v>
+        <v>340</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>360</v>
+        <v>174</v>
       </c>
       <c r="F70" s="6" t="s">
-        <v>361</v>
-      </c>
-      <c r="G70" s="1" t="str">
-        <f>VLOOKUP(A70,[1]Sheet2!A:B,2,0)</f>
-        <v>Sara</v>
+        <v>175</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="H70" s="12">
-        <f>VLOOKUP(A70,[1]Sheet2!A:E,5,0)</f>
         <v>60000000</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>356</v>
+        <v>337</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>356</v>
+        <v>337</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>362</v>
+        <v>341</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>363</v>
+        <v>342</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>360</v>
+        <v>174</v>
       </c>
       <c r="F71" s="6" t="s">
-        <v>361</v>
-      </c>
-      <c r="G71" s="1" t="str">
-        <f>VLOOKUP(A71,[1]Sheet2!A:B,2,0)</f>
-        <v>Sara</v>
+        <v>175</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="H71" s="12">
-        <f>VLOOKUP(A71,[1]Sheet2!A:E,5,0)</f>
         <v>60000000</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>364</v>
+        <v>343</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>364</v>
+        <v>343</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>365</v>
+        <v>344</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>366</v>
+        <v>345</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>367</v>
+        <v>93</v>
       </c>
       <c r="F72" s="6" t="s">
-        <v>368</v>
-      </c>
-      <c r="G72" s="1" t="str">
-        <f>VLOOKUP(A72,[1]Sheet2!A:B,2,0)</f>
-        <v>Naser</v>
+        <v>94</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="H72" s="12">
-        <f>VLOOKUP(A72,[1]Sheet2!A:E,5,0)</f>
         <v>427000000</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>364</v>
+        <v>343</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>369</v>
+        <v>346</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>370</v>
+        <v>347</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>371</v>
+        <v>348</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>367</v>
+        <v>93</v>
       </c>
       <c r="F73" s="6" t="s">
-        <v>368</v>
-      </c>
-      <c r="G73" s="1" t="str">
-        <f>VLOOKUP(A73,[1]Sheet2!A:B,2,0)</f>
-        <v>Naser</v>
+        <v>94</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="H73" s="12">
-        <f>VLOOKUP(A73,[1]Sheet2!A:E,5,0)</f>
         <v>427000000</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>364</v>
+        <v>343</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>372</v>
+        <v>349</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>373</v>
+        <v>350</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>374</v>
+        <v>351</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>367</v>
+        <v>93</v>
       </c>
       <c r="F74" s="6" t="s">
-        <v>368</v>
-      </c>
-      <c r="G74" s="1" t="str">
-        <f>VLOOKUP(A74,[1]Sheet2!A:B,2,0)</f>
-        <v>Naser</v>
+        <v>94</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="H74" s="12">
-        <f>VLOOKUP(A74,[1]Sheet2!A:E,5,0)</f>
         <v>427000000</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>375</v>
+        <v>352</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>376</v>
+        <v>353</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>377</v>
+        <v>354</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>378</v>
+        <v>355</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>379</v>
+        <v>187</v>
       </c>
       <c r="F75" s="6" t="s">
-        <v>380</v>
-      </c>
-      <c r="G75" s="1" t="str">
-        <f>VLOOKUP(A75,[1]Sheet2!A:B,2,0)</f>
-        <v>Nastaran</v>
+        <v>188</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>865</v>
       </c>
       <c r="H75" s="12">
-        <f>VLOOKUP(A75,[1]Sheet2!A:E,5,0)</f>
         <v>46200000</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>375</v>
+        <v>352</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>375</v>
+        <v>352</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>381</v>
+        <v>356</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>382</v>
+        <v>357</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>379</v>
+        <v>187</v>
       </c>
       <c r="F76" s="6" t="s">
-        <v>380</v>
-      </c>
-      <c r="G76" s="1" t="str">
-        <f>VLOOKUP(A76,[1]Sheet2!A:B,2,0)</f>
-        <v>Nastaran</v>
+        <v>188</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>865</v>
       </c>
       <c r="H76" s="12">
-        <f>VLOOKUP(A76,[1]Sheet2!A:E,5,0)</f>
         <v>46200000</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
-        <v>383</v>
+        <v>358</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>384</v>
+        <v>359</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>385</v>
+        <v>360</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>386</v>
+        <v>361</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>387</v>
+        <v>875</v>
       </c>
       <c r="F77" s="6" t="s">
-        <v>388</v>
+        <v>876</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>13</v>
+        <v>877</v>
       </c>
       <c r="H77" s="12">
-        <f>VLOOKUP(A77,[1]Sheet2!A:E,5,0)</f>
         <v>46200000</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
-        <v>389</v>
+        <v>362</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>390</v>
+        <v>363</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>391</v>
+        <v>364</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>392</v>
+        <v>365</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>39</v>
@@ -6515,27 +5442,25 @@
       <c r="F78" s="31" t="s">
         <v>40</v>
       </c>
-      <c r="G78" s="1" t="str">
-        <f>VLOOKUP(A78,[1]Sheet2!A:B,2,0)</f>
-        <v>Sara</v>
+      <c r="G78" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="H78" s="12">
-        <f>VLOOKUP(A78,[1]Sheet2!A:E,5,0)</f>
         <v>75000000</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
-        <v>389</v>
+        <v>362</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>389</v>
+        <v>362</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>393</v>
+        <v>366</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>394</v>
+        <v>367</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>39</v>
@@ -6543,3239 +5468,3134 @@
       <c r="F79" s="31" t="s">
         <v>40</v>
       </c>
-      <c r="G79" s="1" t="str">
-        <f>VLOOKUP(A79,[1]Sheet2!A:B,2,0)</f>
-        <v>Sara</v>
+      <c r="G79" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="H79" s="12">
-        <f>VLOOKUP(A79,[1]Sheet2!A:E,5,0)</f>
         <v>75000000</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>395</v>
+        <v>368</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>396</v>
+        <v>369</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>397</v>
+        <v>370</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>398</v>
+        <v>371</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>399</v>
+        <v>88</v>
       </c>
       <c r="F80" s="6" t="s">
-        <v>400</v>
+        <v>89</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>13</v>
+        <v>877</v>
       </c>
       <c r="H80" s="12">
-        <f>VLOOKUP(A80,[1]Sheet2!A:E,5,0)</f>
         <v>41580000</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
-        <v>401</v>
+        <v>372</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>402</v>
+        <v>373</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>403</v>
+        <v>374</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>404</v>
+        <v>375</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>405</v>
+        <v>129</v>
       </c>
       <c r="F81" s="6" t="s">
-        <v>406</v>
+        <v>130</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>13</v>
+        <v>877</v>
       </c>
       <c r="H81" s="12">
-        <f>VLOOKUP(A81,[1]Sheet2!A:E,5,0)</f>
         <v>6600000</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>407</v>
+        <v>376</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>408</v>
+        <v>377</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>409</v>
+        <v>378</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>410</v>
+        <v>379</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>411</v>
+        <v>523</v>
       </c>
       <c r="F82" s="6" t="s">
-        <v>412</v>
+        <v>93</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>13</v>
+        <v>877</v>
       </c>
       <c r="H82" s="12">
-        <f>VLOOKUP(A82,[1]Sheet2!A:E,5,0)</f>
         <v>49500000</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
-        <v>413</v>
+        <v>380</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>414</v>
+        <v>381</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>415</v>
+        <v>382</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>416</v>
+        <v>383</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>417</v>
+        <v>432</v>
       </c>
       <c r="F83" s="6" t="s">
-        <v>418</v>
-      </c>
-      <c r="G83" s="1" t="str">
-        <f>VLOOKUP(A83,[1]Sheet2!A:B,2,0)</f>
-        <v>Nastaran</v>
+        <v>878</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>865</v>
       </c>
       <c r="H83" s="12">
-        <f>VLOOKUP(A83,[1]Sheet2!A:E,5,0)</f>
         <v>33000000</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
-        <v>419</v>
+        <v>384</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>420</v>
+        <v>385</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>421</v>
+        <v>386</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>422</v>
+        <v>387</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>423</v>
+        <v>289</v>
       </c>
       <c r="F84" s="6" t="s">
-        <v>424</v>
-      </c>
-      <c r="G84" s="1" t="str">
-        <f>VLOOKUP(A84,[1]Sheet2!A:B,2,0)</f>
-        <v>Nastaran</v>
+        <v>873</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>865</v>
       </c>
       <c r="H84" s="12">
-        <f>VLOOKUP(A84,[1]Sheet2!A:E,5,0)</f>
         <v>23100000</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
-        <v>419</v>
+        <v>384</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>425</v>
+        <v>388</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>426</v>
+        <v>389</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>427</v>
+        <v>390</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>423</v>
+        <v>289</v>
       </c>
       <c r="F85" s="6" t="s">
-        <v>424</v>
-      </c>
-      <c r="G85" s="1" t="str">
-        <f>VLOOKUP(A85,[1]Sheet2!A:B,2,0)</f>
-        <v>Nastaran</v>
+        <v>873</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>865</v>
       </c>
       <c r="H85" s="12">
-        <f>VLOOKUP(A85,[1]Sheet2!A:E,5,0)</f>
         <v>23100000</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
-        <v>428</v>
+        <v>391</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>429</v>
+        <v>392</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>430</v>
+        <v>393</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>431</v>
+        <v>394</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>432</v>
+        <v>289</v>
       </c>
       <c r="F86" s="6" t="s">
-        <v>433</v>
+        <v>873</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>13</v>
+        <v>877</v>
       </c>
       <c r="H86" s="12">
-        <f>VLOOKUP(A86,[1]Sheet2!A:E,5,0)</f>
         <v>30000000</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
-        <v>434</v>
+        <v>395</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>435</v>
+        <v>396</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>436</v>
+        <v>397</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="E87" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="F87" s="6" t="s">
-        <v>439</v>
-      </c>
+        <v>398</v>
+      </c>
+      <c r="E87" s="1"/>
+      <c r="F87" s="6"/>
       <c r="G87" s="1"/>
       <c r="H87" s="12"/>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
-        <v>440</v>
+        <v>399</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>441</v>
+        <v>400</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>442</v>
+        <v>401</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>443</v>
+        <v>402</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>444</v>
+        <v>118</v>
       </c>
       <c r="F88" s="6" t="s">
-        <v>445</v>
-      </c>
-      <c r="G88" s="1" t="str">
-        <f>VLOOKUP(A88,[1]Sheet2!A:B,2,0)</f>
-        <v>Nastaran</v>
+        <v>119</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>865</v>
       </c>
       <c r="H88" s="12">
-        <f>VLOOKUP(A88,[1]Sheet2!A:E,5,0)</f>
         <v>170000000</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
-        <v>440</v>
+        <v>399</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>446</v>
+        <v>403</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>447</v>
+        <v>404</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>448</v>
+        <v>405</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>444</v>
+        <v>118</v>
       </c>
       <c r="F89" s="6" t="s">
-        <v>445</v>
-      </c>
-      <c r="G89" s="1" t="str">
-        <f>VLOOKUP(A89,[1]Sheet2!A:B,2,0)</f>
-        <v>Nastaran</v>
+        <v>119</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>865</v>
       </c>
       <c r="H89" s="12">
-        <f>VLOOKUP(A89,[1]Sheet2!A:E,5,0)</f>
         <v>170000000</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
-        <v>449</v>
+        <v>406</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>450</v>
+        <v>407</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>451</v>
+        <v>408</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>452</v>
-      </c>
-      <c r="E90" s="1" t="s">
-        <v>453</v>
-      </c>
-      <c r="F90" s="6" t="s">
-        <v>454</v>
-      </c>
+        <v>409</v>
+      </c>
+      <c r="E90" s="1"/>
+      <c r="F90" s="6"/>
       <c r="G90" s="1"/>
       <c r="H90" s="12"/>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
-        <v>455</v>
+        <v>410</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>456</v>
+        <v>411</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>457</v>
+        <v>412</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="E91" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="F91" s="6" t="s">
-        <v>46</v>
-      </c>
+        <v>413</v>
+      </c>
+      <c r="E91" s="1"/>
+      <c r="F91" s="6"/>
       <c r="G91" s="1"/>
       <c r="H91" s="12"/>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
-        <v>459</v>
+        <v>414</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>459</v>
+        <v>414</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>460</v>
+        <v>415</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>461</v>
+        <v>416</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>462</v>
+        <v>867</v>
       </c>
       <c r="F92" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G92" s="1" t="str">
-        <f>VLOOKUP(A92,[1]Sheet2!A:B,2,0)</f>
-        <v>Nastaran</v>
+        <v>868</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>865</v>
       </c>
       <c r="H92" s="12">
-        <f>VLOOKUP(A92,[1]Sheet2!A:E,5,0)</f>
         <v>6600000</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
-        <v>463</v>
+        <v>417</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>463</v>
+        <v>417</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>464</v>
+        <v>418</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>465</v>
+        <v>419</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>466</v>
+        <v>423</v>
       </c>
       <c r="F93" s="6" t="s">
-        <v>467</v>
-      </c>
-      <c r="G93" s="1" t="str">
-        <f>VLOOKUP(A93,[1]Sheet2!A:B,2,0)</f>
-        <v>Nastaran</v>
+        <v>424</v>
+      </c>
+      <c r="G93" s="1" t="s">
+        <v>865</v>
       </c>
       <c r="H93" s="12">
-        <f>VLOOKUP(A93,[1]Sheet2!A:E,5,0)</f>
         <v>72600000</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
-        <v>468</v>
+        <v>420</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>468</v>
+        <v>420</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>469</v>
+        <v>421</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>470</v>
+        <v>422</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>471</v>
+        <v>879</v>
       </c>
       <c r="F94" s="36" t="s">
-        <v>472</v>
-      </c>
-      <c r="G94" s="1" t="str">
-        <f>VLOOKUP(A94,[1]Sheet2!A:B,2,0)</f>
-        <v>Nastaran</v>
+        <v>880</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>865</v>
       </c>
       <c r="H94" s="12">
-        <f>VLOOKUP(A94,[1]Sheet2!A:E,5,0)</f>
         <v>49500000</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
-        <v>473</v>
+        <v>425</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>473</v>
+        <v>425</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>474</v>
+        <v>426</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>475</v>
+        <v>427</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="F95" s="28" t="s">
-        <v>255</v>
-      </c>
-      <c r="G95" s="1" t="str">
-        <f>VLOOKUP(A95,[1]Sheet2!A:B,2,0)</f>
-        <v>Sara</v>
+        <v>262</v>
+      </c>
+      <c r="G95" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="H95" s="12">
-        <f>VLOOKUP(A95,[1]Sheet2!A:E,5,0)</f>
         <v>34000000</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
-        <v>476</v>
+        <v>428</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>477</v>
+        <v>429</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>478</v>
+        <v>430</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>479</v>
-      </c>
-      <c r="E96" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="F96" s="6" t="s">
-        <v>481</v>
-      </c>
+        <v>431</v>
+      </c>
+      <c r="E96" s="1"/>
+      <c r="F96" s="6"/>
       <c r="G96" s="1"/>
       <c r="H96" s="12"/>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
-        <v>482</v>
+        <v>433</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>483</v>
+        <v>434</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>484</v>
+        <v>435</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>485</v>
+        <v>436</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>486</v>
+        <v>613</v>
       </c>
       <c r="F97" s="6" t="s">
-        <v>487</v>
-      </c>
-      <c r="G97" s="1" t="str">
-        <f>VLOOKUP(A97,[1]Sheet2!A:B,2,0)</f>
-        <v>Naser</v>
+        <v>614</v>
+      </c>
+      <c r="G97" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="H97" s="12">
-        <f>VLOOKUP(A97,[1]Sheet2!A:E,5,0)</f>
         <v>206000000</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
-        <v>482</v>
+        <v>433</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>488</v>
+        <v>438</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>489</v>
+        <v>439</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>490</v>
+        <v>440</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>486</v>
+        <v>613</v>
       </c>
       <c r="F98" s="6" t="s">
-        <v>487</v>
-      </c>
-      <c r="G98" s="1" t="str">
-        <f>VLOOKUP(A98,[1]Sheet2!A:B,2,0)</f>
-        <v>Naser</v>
+        <v>614</v>
+      </c>
+      <c r="G98" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="H98" s="12">
-        <f>VLOOKUP(A98,[1]Sheet2!A:E,5,0)</f>
         <v>206000000</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
-        <v>491</v>
+        <v>441</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>492</v>
+        <v>442</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>493</v>
+        <v>443</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>494</v>
+        <v>444</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>123</v>
+        <v>461</v>
       </c>
       <c r="F99" s="20" t="s">
-        <v>124</v>
+        <v>462</v>
       </c>
       <c r="G99" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H99" s="12">
-        <f>VLOOKUP(A99,[1]Sheet2!A:E,5,0)</f>
         <v>60000000</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
-        <v>495</v>
+        <v>445</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>496</v>
+        <v>446</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>497</v>
+        <v>447</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>498</v>
+        <v>448</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>499</v>
+        <v>267</v>
       </c>
       <c r="F100" s="37" t="s">
-        <v>500</v>
-      </c>
-      <c r="G100" s="1" t="str">
-        <f>VLOOKUP(A100,[1]Sheet2!A:B,2,0)</f>
-        <v>Nastaran</v>
+        <v>268</v>
+      </c>
+      <c r="G100" s="1" t="s">
+        <v>865</v>
       </c>
       <c r="H100" s="12">
-        <f>VLOOKUP(A100,[1]Sheet2!A:E,5,0)</f>
         <v>76000000</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
-        <v>501</v>
+        <v>449</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>501</v>
+        <v>449</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>502</v>
+        <v>450</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>503</v>
+        <v>451</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>504</v>
+        <v>244</v>
       </c>
       <c r="F101" s="38" t="s">
-        <v>505</v>
+        <v>245</v>
       </c>
       <c r="G101" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H101" s="12">
-        <f>VLOOKUP(A101,[1]Sheet2!A:E,5,0)</f>
         <v>42900000</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
-        <v>506</v>
+        <v>454</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>507</v>
+        <v>455</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>508</v>
+        <v>456</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>509</v>
+        <v>457</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>510</v>
+        <v>881</v>
       </c>
       <c r="F102" s="6" t="s">
-        <v>511</v>
-      </c>
-      <c r="G102" s="1" t="str">
-        <f>VLOOKUP(A102,[1]Sheet2!A:B,2,0)</f>
-        <v>Nastaran</v>
+        <v>198</v>
+      </c>
+      <c r="G102" s="1" t="s">
+        <v>865</v>
       </c>
       <c r="H102" s="12">
-        <f>VLOOKUP(A102,[1]Sheet2!A:E,5,0)</f>
         <v>39600000</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
-        <v>512</v>
+        <v>458</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>512</v>
+        <v>458</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>513</v>
+        <v>459</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>514</v>
-      </c>
-      <c r="E103" s="1" t="s">
-        <v>515</v>
-      </c>
-      <c r="F103" s="39" t="s">
-        <v>516</v>
-      </c>
+        <v>460</v>
+      </c>
+      <c r="E103" s="1"/>
+      <c r="F103" s="39"/>
       <c r="G103" s="1"/>
       <c r="H103" s="12"/>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
-        <v>517</v>
+        <v>463</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>517</v>
+        <v>463</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>518</v>
+        <v>464</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="E104" s="1" t="s">
-        <v>504</v>
-      </c>
-      <c r="F104" s="38" t="s">
-        <v>505</v>
-      </c>
+        <v>465</v>
+      </c>
+      <c r="E104" s="1"/>
+      <c r="F104" s="38"/>
       <c r="G104" s="1"/>
       <c r="H104" s="12"/>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
-        <v>520</v>
+        <v>466</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>521</v>
+        <v>467</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>522</v>
+        <v>468</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>523</v>
-      </c>
-      <c r="E105" s="1" t="s">
-        <v>524</v>
-      </c>
-      <c r="F105" s="6" t="s">
-        <v>525</v>
-      </c>
+        <v>469</v>
+      </c>
+      <c r="E105" s="1"/>
+      <c r="F105" s="6"/>
       <c r="G105" s="1"/>
       <c r="H105" s="12"/>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
-        <v>520</v>
+        <v>466</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>526</v>
+        <v>470</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>527</v>
+        <v>471</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="E106" s="1" t="s">
-        <v>524</v>
-      </c>
-      <c r="F106" s="6" t="s">
-        <v>525</v>
-      </c>
+        <v>472</v>
+      </c>
+      <c r="E106" s="1"/>
+      <c r="F106" s="6"/>
       <c r="G106" s="1"/>
       <c r="H106" s="12"/>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
-        <v>520</v>
+        <v>466</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>529</v>
+        <v>473</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>530</v>
+        <v>474</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="E107" s="1" t="s">
-        <v>524</v>
-      </c>
-      <c r="F107" s="6" t="s">
-        <v>525</v>
-      </c>
+        <v>475</v>
+      </c>
+      <c r="E107" s="1"/>
+      <c r="F107" s="6"/>
       <c r="G107" s="1"/>
       <c r="H107" s="12"/>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
-        <v>520</v>
+        <v>466</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>532</v>
+        <v>476</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>533</v>
+        <v>477</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="E108" s="1" t="s">
-        <v>524</v>
-      </c>
-      <c r="F108" s="6" t="s">
-        <v>525</v>
-      </c>
+        <v>478</v>
+      </c>
+      <c r="E108" s="1"/>
+      <c r="F108" s="6"/>
       <c r="G108" s="1"/>
       <c r="H108" s="12"/>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
-        <v>520</v>
+        <v>466</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>535</v>
+        <v>479</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>536</v>
+        <v>480</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>537</v>
-      </c>
-      <c r="E109" s="1" t="s">
-        <v>524</v>
-      </c>
-      <c r="F109" s="6" t="s">
-        <v>525</v>
-      </c>
+        <v>481</v>
+      </c>
+      <c r="E109" s="1"/>
+      <c r="F109" s="6"/>
       <c r="G109" s="1"/>
       <c r="H109" s="12"/>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
-        <v>520</v>
+        <v>466</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>538</v>
+        <v>482</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>539</v>
+        <v>483</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>540</v>
-      </c>
-      <c r="E110" s="1" t="s">
-        <v>524</v>
-      </c>
-      <c r="F110" s="6" t="s">
-        <v>525</v>
-      </c>
+        <v>484</v>
+      </c>
+      <c r="E110" s="1"/>
+      <c r="F110" s="6"/>
       <c r="G110" s="1"/>
       <c r="H110" s="12"/>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
-        <v>520</v>
+        <v>466</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>541</v>
+        <v>485</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>542</v>
+        <v>486</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="E111" s="1" t="s">
-        <v>524</v>
-      </c>
-      <c r="F111" s="6" t="s">
-        <v>525</v>
-      </c>
+        <v>487</v>
+      </c>
+      <c r="E111" s="1"/>
+      <c r="F111" s="6"/>
       <c r="G111" s="1"/>
       <c r="H111" s="12"/>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
-        <v>520</v>
+        <v>466</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>544</v>
+        <v>488</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>545</v>
+        <v>489</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="E112" s="1" t="s">
-        <v>524</v>
-      </c>
-      <c r="F112" s="6" t="s">
-        <v>525</v>
-      </c>
+        <v>490</v>
+      </c>
+      <c r="E112" s="1"/>
+      <c r="F112" s="6"/>
       <c r="G112" s="1"/>
       <c r="H112" s="12"/>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
-        <v>520</v>
+        <v>466</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>547</v>
+        <v>491</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>548</v>
+        <v>492</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>549</v>
-      </c>
-      <c r="E113" s="1" t="s">
-        <v>524</v>
-      </c>
-      <c r="F113" s="6" t="s">
-        <v>525</v>
-      </c>
+        <v>493</v>
+      </c>
+      <c r="E113" s="1"/>
+      <c r="F113" s="6"/>
       <c r="G113" s="1"/>
       <c r="H113" s="12"/>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
-        <v>550</v>
+        <v>494</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>551</v>
+        <v>495</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>552</v>
+        <v>496</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>553</v>
-      </c>
-      <c r="E114" s="1" t="s">
-        <v>554</v>
-      </c>
-      <c r="F114" s="40" t="s">
-        <v>555</v>
-      </c>
+        <v>497</v>
+      </c>
+      <c r="E114" s="1"/>
+      <c r="F114" s="40"/>
       <c r="G114" s="1"/>
       <c r="H114" s="12"/>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
-        <v>556</v>
+        <v>498</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>557</v>
+        <v>499</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>558</v>
+        <v>500</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>559</v>
+        <v>501</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>560</v>
+        <v>543</v>
       </c>
       <c r="F115" s="6" t="s">
-        <v>510</v>
-      </c>
-      <c r="G115" s="1" t="str">
-        <f>VLOOKUP(A115,[1]Sheet2!A:B,2,0)</f>
-        <v>Naser</v>
+        <v>869</v>
+      </c>
+      <c r="G115" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="H115" s="12">
-        <f>VLOOKUP(A115,[1]Sheet2!A:E,5,0)</f>
         <v>99000000</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
-        <v>556</v>
+        <v>498</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>561</v>
+        <v>502</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>562</v>
+        <v>503</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>563</v>
+        <v>504</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>560</v>
+        <v>543</v>
       </c>
       <c r="F116" s="6" t="s">
-        <v>510</v>
-      </c>
-      <c r="G116" s="1" t="str">
-        <f>VLOOKUP(A116,[1]Sheet2!A:B,2,0)</f>
-        <v>Naser</v>
+        <v>869</v>
+      </c>
+      <c r="G116" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="H116" s="12">
-        <f>VLOOKUP(A116,[1]Sheet2!A:E,5,0)</f>
         <v>99000000</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
-        <v>556</v>
+        <v>498</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>564</v>
+        <v>505</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>565</v>
+        <v>506</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>566</v>
+        <v>507</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>560</v>
+        <v>543</v>
       </c>
       <c r="F117" s="6" t="s">
-        <v>510</v>
-      </c>
-      <c r="G117" s="1" t="str">
-        <f>VLOOKUP(A117,[1]Sheet2!A:B,2,0)</f>
-        <v>Naser</v>
+        <v>869</v>
+      </c>
+      <c r="G117" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="H117" s="12">
-        <f>VLOOKUP(A117,[1]Sheet2!A:E,5,0)</f>
         <v>99000000</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
-        <v>567</v>
+        <v>508</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>568</v>
+        <v>509</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>569</v>
+        <v>510</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>570</v>
+        <v>511</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>169</v>
+        <v>623</v>
       </c>
       <c r="F118" s="13" t="s">
-        <v>571</v>
-      </c>
-      <c r="G118" s="1" t="str">
-        <f>VLOOKUP(A118,[1]Sheet2!A:B,2,0)</f>
-        <v>Naser</v>
+        <v>624</v>
+      </c>
+      <c r="G118" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="H118" s="12">
-        <f>VLOOKUP(A118,[1]Sheet2!A:E,5,0)</f>
         <v>44000000</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
-        <v>572</v>
+        <v>513</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>572</v>
+        <v>513</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>573</v>
+        <v>514</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>574</v>
+        <v>515</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>575</v>
+        <v>192</v>
       </c>
       <c r="F119" s="6" t="s">
-        <v>576</v>
-      </c>
-      <c r="G119" s="1" t="str">
-        <f>VLOOKUP(A119,[1]Sheet2!A:B,2,0)</f>
-        <v>Sanam</v>
+        <v>193</v>
+      </c>
+      <c r="G119" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="H119" s="12">
-        <f>VLOOKUP(A119,[1]Sheet2!A:E,5,0)</f>
         <v>30000000</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
-        <v>577</v>
+        <v>516</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>578</v>
+        <v>517</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>579</v>
+        <v>518</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>580</v>
+        <v>519</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>581</v>
+        <v>527</v>
       </c>
       <c r="F120" s="6" t="s">
-        <v>582</v>
+        <v>528</v>
       </c>
       <c r="G120" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H120" s="12">
-        <f>VLOOKUP(A120,[1]Sheet2!A:E,5,0)</f>
         <v>29700000</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
-        <v>583</v>
+        <v>520</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>583</v>
+        <v>520</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>584</v>
+        <v>521</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>585</v>
+        <v>522</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>586</v>
+        <v>613</v>
       </c>
       <c r="F121" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="G121" s="1" t="str">
-        <f>VLOOKUP(A121,[1]Sheet2!A:B,2,0)</f>
-        <v>Sanam</v>
+        <v>614</v>
+      </c>
+      <c r="G121" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="H121" s="12">
-        <f>VLOOKUP(A121,[1]Sheet2!A:E,5,0)</f>
         <v>80000000</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
-        <v>587</v>
+        <v>524</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>587</v>
+        <v>524</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>588</v>
+        <v>525</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>589</v>
+        <v>526</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>590</v>
+        <v>39</v>
       </c>
       <c r="F122" s="41" t="s">
-        <v>591</v>
+        <v>40</v>
       </c>
       <c r="G122" s="1" t="s">
         <v>41</v>
       </c>
       <c r="H122" s="12">
-        <f>VLOOKUP(A122,[1]Sheet2!A:E,5,0)</f>
         <v>30000000</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
-        <v>592</v>
+        <v>529</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>592</v>
+        <v>529</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>593</v>
+        <v>530</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>594</v>
-      </c>
-      <c r="E123" s="1" t="s">
-        <v>595</v>
-      </c>
-      <c r="F123" s="6" t="s">
-        <v>215</v>
-      </c>
+        <v>531</v>
+      </c>
+      <c r="E123" s="1"/>
+      <c r="F123" s="6"/>
       <c r="G123" s="1"/>
       <c r="H123" s="12"/>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
-        <v>596</v>
+        <v>532</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>596</v>
+        <v>532</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>597</v>
+        <v>533</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>598</v>
+        <v>534</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>303</v>
+        <v>289</v>
       </c>
       <c r="F124" s="32" t="s">
-        <v>304</v>
-      </c>
-      <c r="G124" s="1" t="str">
-        <f>VLOOKUP(A124,[1]Sheet2!A:B,2,0)</f>
-        <v>Nastaran</v>
+        <v>873</v>
+      </c>
+      <c r="G124" s="1" t="s">
+        <v>865</v>
       </c>
       <c r="H124" s="12">
-        <f>VLOOKUP(A124,[1]Sheet2!A:E,5,0)</f>
         <v>33000000</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
-        <v>599</v>
+        <v>535</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>600</v>
+        <v>536</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>601</v>
+        <v>537</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>602</v>
+        <v>538</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>204</v>
+        <v>568</v>
       </c>
       <c r="F125" s="26" t="s">
-        <v>199</v>
-      </c>
-      <c r="G125" s="1" t="str">
-        <f>VLOOKUP(A125,[1]Sheet2!A:B,2,0)</f>
-        <v>Sanam</v>
+        <v>569</v>
+      </c>
+      <c r="G125" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="H125" s="12">
-        <f>VLOOKUP(A125,[1]Sheet2!A:E,5,0)</f>
         <v>40000000</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
-        <v>603</v>
+        <v>539</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>604</v>
+        <v>540</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>605</v>
+        <v>541</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>606</v>
+        <v>542</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>210</v>
+        <v>882</v>
       </c>
       <c r="F126" s="6" t="s">
-        <v>607</v>
+        <v>872</v>
       </c>
       <c r="G126" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H126" s="12">
-        <f>VLOOKUP(A126,[1]Sheet2!A:E,5,0)</f>
         <v>46200000</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
-        <v>608</v>
+        <v>544</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>609</v>
+        <v>545</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>610</v>
+        <v>546</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>611</v>
-      </c>
-      <c r="E127" s="1" t="s">
-        <v>612</v>
-      </c>
-      <c r="F127" s="6" t="s">
-        <v>613</v>
-      </c>
+        <v>547</v>
+      </c>
+      <c r="E127" s="1"/>
+      <c r="F127" s="6"/>
       <c r="G127" s="1"/>
       <c r="H127" s="12"/>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
-        <v>614</v>
+        <v>548</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>614</v>
+        <v>548</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>615</v>
+        <v>549</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>616</v>
+        <v>550</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>617</v>
+        <v>52</v>
       </c>
       <c r="F128" s="6" t="s">
-        <v>618</v>
+        <v>53</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>13</v>
+        <v>877</v>
       </c>
       <c r="H128" s="12">
-        <f>VLOOKUP(A128,[1]Sheet2!A:E,5,0)</f>
         <v>58000000</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A129" s="1" t="s">
-        <v>619</v>
+        <v>551</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>620</v>
+        <v>552</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>621</v>
+        <v>553</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>622</v>
-      </c>
-      <c r="E129" s="1" t="s">
-        <v>623</v>
-      </c>
-      <c r="F129" s="6" t="s">
-        <v>624</v>
-      </c>
+        <v>554</v>
+      </c>
+      <c r="E129" s="1"/>
+      <c r="F129" s="6"/>
       <c r="G129" s="1"/>
       <c r="H129" s="12"/>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
-        <v>625</v>
+        <v>555</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>625</v>
+        <v>555</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>626</v>
+        <v>556</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>627</v>
+        <v>557</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>623</v>
+        <v>883</v>
       </c>
       <c r="F130" s="6" t="s">
-        <v>624</v>
+        <v>884</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>13</v>
+        <v>877</v>
       </c>
       <c r="H130" s="12">
-        <f>VLOOKUP(A130,[1]Sheet2!A:E,5,0)</f>
         <v>82500000</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="s">
-        <v>625</v>
+        <v>555</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>628</v>
+        <v>558</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>629</v>
+        <v>559</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>630</v>
+        <v>560</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>623</v>
+        <v>883</v>
       </c>
       <c r="F131" s="6" t="s">
-        <v>624</v>
+        <v>884</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>13</v>
+        <v>877</v>
       </c>
       <c r="H131" s="12">
-        <f>VLOOKUP(A131,[1]Sheet2!A:E,5,0)</f>
         <v>82500000</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
-        <v>625</v>
+        <v>555</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>631</v>
+        <v>561</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>632</v>
+        <v>562</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>633</v>
+        <v>563</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>623</v>
+        <v>883</v>
       </c>
       <c r="F132" s="6" t="s">
-        <v>624</v>
+        <v>884</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>13</v>
+        <v>877</v>
       </c>
       <c r="H132" s="12">
-        <f>VLOOKUP(A132,[1]Sheet2!A:E,5,0)</f>
         <v>82500000</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A133" s="1" t="s">
-        <v>634</v>
+        <v>564</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>635</v>
+        <v>565</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>636</v>
+        <v>566</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>637</v>
-      </c>
-      <c r="E133" s="1" t="s">
-        <v>638</v>
-      </c>
-      <c r="F133" s="42" t="s">
-        <v>639</v>
-      </c>
+        <v>567</v>
+      </c>
+      <c r="E133" s="1"/>
+      <c r="F133" s="42"/>
       <c r="G133" s="1"/>
       <c r="H133" s="12"/>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
-        <v>640</v>
+        <v>570</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>641</v>
+        <v>571</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>642</v>
+        <v>572</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>643</v>
+        <v>573</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>71</v>
+        <v>12</v>
       </c>
       <c r="F134" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="G134" s="1"/>
-      <c r="H134" s="12"/>
+        <v>885</v>
+      </c>
+      <c r="G134" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H134" s="12">
+        <v>44000000</v>
+      </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A135" s="1" t="s">
-        <v>644</v>
+        <v>574</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>644</v>
+        <v>574</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>645</v>
+        <v>575</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>646</v>
+        <v>576</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>647</v>
+        <v>39</v>
       </c>
       <c r="F135" s="43" t="s">
-        <v>648</v>
-      </c>
-      <c r="G135" s="1"/>
-      <c r="H135" s="12"/>
+        <v>40</v>
+      </c>
+      <c r="G135" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H135" s="12">
+        <v>60000000</v>
+      </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
-        <v>649</v>
+        <v>577</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>649</v>
+        <v>577</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>650</v>
+        <v>578</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>651</v>
-      </c>
-      <c r="E136" s="1" t="s">
-        <v>652</v>
-      </c>
-      <c r="F136" s="44" t="s">
-        <v>653</v>
-      </c>
+        <v>579</v>
+      </c>
+      <c r="E136" s="1"/>
+      <c r="F136" s="44"/>
       <c r="G136" s="1"/>
       <c r="H136" s="12"/>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="s">
-        <v>654</v>
+        <v>580</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>655</v>
+        <v>581</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>656</v>
+        <v>582</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>657</v>
+        <v>583</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>215</v>
+        <v>623</v>
       </c>
       <c r="F137" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="G137" s="1"/>
-      <c r="H137" s="12"/>
+        <v>624</v>
+      </c>
+      <c r="G137" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H137" s="12">
+        <v>95000000</v>
+      </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
-        <v>658</v>
+        <v>584</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>659</v>
+        <v>585</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>660</v>
+        <v>586</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>661</v>
+        <v>587</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>487</v>
+        <v>213</v>
       </c>
       <c r="F138" s="45" t="s">
-        <v>60</v>
-      </c>
-      <c r="G138" s="1"/>
-      <c r="H138" s="12"/>
+        <v>214</v>
+      </c>
+      <c r="G138" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H138" s="12">
+        <v>82500000</v>
+      </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A139" s="1" t="s">
-        <v>658</v>
+        <v>584</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>662</v>
+        <v>588</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>663</v>
+        <v>589</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>664</v>
+        <v>590</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>487</v>
+        <v>213</v>
       </c>
       <c r="F139" s="45" t="s">
-        <v>60</v>
-      </c>
-      <c r="G139" s="1"/>
-      <c r="H139" s="12"/>
+        <v>214</v>
+      </c>
+      <c r="G139" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H139" s="12">
+        <v>82500000</v>
+      </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
-        <v>665</v>
+        <v>591</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>666</v>
+        <v>592</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>667</v>
+        <v>593</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>668</v>
+        <v>594</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>669</v>
+        <v>294</v>
       </c>
       <c r="F140" s="6" t="s">
-        <v>670</v>
-      </c>
-      <c r="G140" s="1"/>
-      <c r="H140" s="12"/>
+        <v>295</v>
+      </c>
+      <c r="G140" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H140" s="12">
+        <v>180000000</v>
+      </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A141" s="1" t="s">
-        <v>665</v>
+        <v>591</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>671</v>
+        <v>595</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>672</v>
+        <v>596</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>673</v>
+        <v>597</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>669</v>
+        <v>294</v>
       </c>
       <c r="F141" s="6" t="s">
-        <v>670</v>
-      </c>
-      <c r="G141" s="1"/>
-      <c r="H141" s="12"/>
+        <v>295</v>
+      </c>
+      <c r="G141" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H141" s="12">
+        <v>180000000</v>
+      </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
-        <v>674</v>
+        <v>598</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>674</v>
+        <v>598</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>675</v>
+        <v>599</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>676</v>
-      </c>
-      <c r="E142" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="F142" s="26" t="s">
-        <v>199</v>
-      </c>
+        <v>600</v>
+      </c>
+      <c r="E142" s="1"/>
+      <c r="F142" s="26"/>
       <c r="G142" s="1"/>
       <c r="H142" s="12"/>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A143" s="1" t="s">
-        <v>677</v>
+        <v>601</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>678</v>
+        <v>602</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>679</v>
+        <v>603</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>680</v>
+        <v>604</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>681</v>
+        <v>623</v>
       </c>
       <c r="F143" s="46" t="s">
-        <v>682</v>
-      </c>
-      <c r="G143" s="1"/>
-      <c r="H143" s="12"/>
+        <v>624</v>
+      </c>
+      <c r="G143" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H143" s="12">
+        <v>60000000</v>
+      </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
-        <v>683</v>
+        <v>605</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>684</v>
+        <v>606</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>685</v>
+        <v>607</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>686</v>
-      </c>
-      <c r="E144" s="1" t="s">
-        <v>687</v>
-      </c>
-      <c r="F144" s="6" t="s">
-        <v>95</v>
-      </c>
+        <v>608</v>
+      </c>
+      <c r="E144" s="1"/>
+      <c r="F144" s="6"/>
       <c r="G144" s="1"/>
       <c r="H144" s="12"/>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A145" s="1" t="s">
-        <v>688</v>
+        <v>609</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>689</v>
+        <v>610</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>690</v>
+        <v>611</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>691</v>
+        <v>612</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>692</v>
+        <v>310</v>
       </c>
       <c r="F145" s="47" t="s">
-        <v>693</v>
-      </c>
-      <c r="G145" s="1"/>
-      <c r="H145" s="12"/>
+        <v>311</v>
+      </c>
+      <c r="G145" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H145" s="12">
+        <v>77000000</v>
+      </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
-        <v>694</v>
+        <v>615</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>695</v>
+        <v>616</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>696</v>
+        <v>617</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>697</v>
-      </c>
-      <c r="E146" s="1" t="s">
-        <v>698</v>
-      </c>
-      <c r="F146" s="6" t="s">
-        <v>699</v>
-      </c>
+        <v>618</v>
+      </c>
+      <c r="E146" s="1"/>
+      <c r="F146" s="6"/>
       <c r="G146" s="1"/>
       <c r="H146" s="12"/>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A147" s="1" t="s">
-        <v>700</v>
+        <v>619</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>701</v>
+        <v>620</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>702</v>
+        <v>621</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>703</v>
-      </c>
-      <c r="E147" s="1" t="s">
-        <v>704</v>
-      </c>
-      <c r="F147" s="48" t="s">
-        <v>705</v>
-      </c>
+        <v>622</v>
+      </c>
+      <c r="E147" s="1"/>
+      <c r="F147" s="48"/>
       <c r="G147" s="1"/>
       <c r="H147" s="12"/>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
-        <v>700</v>
+        <v>619</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>706</v>
+        <v>625</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>707</v>
+        <v>626</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>708</v>
-      </c>
-      <c r="E148" s="1" t="s">
-        <v>704</v>
-      </c>
-      <c r="F148" s="48" t="s">
-        <v>705</v>
-      </c>
+        <v>627</v>
+      </c>
+      <c r="E148" s="1"/>
+      <c r="F148" s="48"/>
       <c r="G148" s="1"/>
       <c r="H148" s="12"/>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A149" s="1" t="s">
-        <v>709</v>
+        <v>628</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>710</v>
+        <v>629</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>711</v>
+        <v>630</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>712</v>
-      </c>
-      <c r="E149" s="1" t="s">
-        <v>713</v>
-      </c>
-      <c r="F149" s="6" t="s">
-        <v>432</v>
-      </c>
+        <v>631</v>
+      </c>
+      <c r="E149" s="1"/>
+      <c r="F149" s="6"/>
       <c r="G149" s="1"/>
       <c r="H149" s="12"/>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
-        <v>714</v>
+        <v>632</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>714</v>
+        <v>632</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>715</v>
+        <v>633</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>716</v>
+        <v>634</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>717</v>
+        <v>294</v>
       </c>
       <c r="F150" s="6" t="s">
-        <v>718</v>
-      </c>
-      <c r="G150" s="1"/>
-      <c r="H150" s="12"/>
+        <v>295</v>
+      </c>
+      <c r="G150" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H150" s="12">
+        <v>330000000</v>
+      </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="s">
-        <v>719</v>
+        <v>635</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>719</v>
+        <v>635</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>720</v>
+        <v>636</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>721</v>
-      </c>
-      <c r="E151" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="F151" s="6" t="s">
-        <v>607</v>
-      </c>
+        <v>637</v>
+      </c>
+      <c r="E151" s="1"/>
+      <c r="F151" s="6"/>
       <c r="G151" s="1"/>
       <c r="H151" s="12"/>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
-        <v>722</v>
+        <v>638</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>722</v>
+        <v>638</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>723</v>
+        <v>639</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>724</v>
+        <v>640</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>595</v>
+        <v>12</v>
       </c>
       <c r="F152" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="G152" s="1"/>
-      <c r="H152" s="12"/>
+        <v>885</v>
+      </c>
+      <c r="G152" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H152" s="12">
+        <v>175000000</v>
+      </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A153" s="1" t="s">
-        <v>722</v>
+        <v>638</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>725</v>
+        <v>641</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>726</v>
+        <v>642</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>727</v>
+        <v>643</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>595</v>
+        <v>12</v>
       </c>
       <c r="F153" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="G153" s="1"/>
-      <c r="H153" s="12"/>
+        <v>885</v>
+      </c>
+      <c r="G153" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H153" s="12">
+        <v>175000000</v>
+      </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="s">
-        <v>722</v>
+        <v>638</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>728</v>
+        <v>644</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>729</v>
+        <v>645</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>730</v>
+        <v>646</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>595</v>
+        <v>12</v>
       </c>
       <c r="F154" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="G154" s="1"/>
-      <c r="H154" s="12"/>
+        <v>885</v>
+      </c>
+      <c r="G154" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H154" s="12">
+        <v>175000000</v>
+      </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A155" s="1" t="s">
-        <v>722</v>
+        <v>638</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>731</v>
+        <v>647</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>732</v>
+        <v>648</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>733</v>
+        <v>649</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>595</v>
+        <v>12</v>
       </c>
       <c r="F155" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="G155" s="1"/>
-      <c r="H155" s="12"/>
+        <v>885</v>
+      </c>
+      <c r="G155" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H155" s="12">
+        <v>175000000</v>
+      </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A156" s="1" t="s">
-        <v>722</v>
+        <v>638</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>734</v>
+        <v>650</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>735</v>
+        <v>651</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>736</v>
+        <v>652</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>595</v>
+        <v>12</v>
       </c>
       <c r="F156" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="G156" s="1"/>
-      <c r="H156" s="12"/>
+        <v>885</v>
+      </c>
+      <c r="G156" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H156" s="12">
+        <v>175000000</v>
+      </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A157" s="1" t="s">
-        <v>737</v>
+        <v>653</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>738</v>
+        <v>654</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>739</v>
+        <v>655</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>740</v>
-      </c>
-      <c r="E157" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="F157" s="16" t="s">
-        <v>96</v>
-      </c>
+        <v>656</v>
+      </c>
+      <c r="E157" s="1"/>
+      <c r="F157" s="16"/>
       <c r="G157" s="1"/>
       <c r="H157" s="12"/>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="s">
-        <v>737</v>
+        <v>653</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>741</v>
+        <v>657</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>742</v>
+        <v>658</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>743</v>
-      </c>
-      <c r="E158" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="F158" s="16" t="s">
-        <v>96</v>
-      </c>
+        <v>659</v>
+      </c>
+      <c r="E158" s="1"/>
+      <c r="F158" s="16"/>
       <c r="G158" s="1"/>
       <c r="H158" s="12"/>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A159" s="1" t="s">
-        <v>737</v>
+        <v>653</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>744</v>
+        <v>660</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>745</v>
+        <v>661</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>746</v>
-      </c>
-      <c r="E159" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="F159" s="16" t="s">
-        <v>96</v>
-      </c>
+        <v>662</v>
+      </c>
+      <c r="E159" s="1"/>
+      <c r="F159" s="16"/>
       <c r="G159" s="1"/>
       <c r="H159" s="12"/>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A160" s="1" t="s">
-        <v>737</v>
+        <v>653</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>747</v>
+        <v>663</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>748</v>
+        <v>664</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>749</v>
-      </c>
-      <c r="E160" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="F160" s="16" t="s">
-        <v>96</v>
-      </c>
+        <v>665</v>
+      </c>
+      <c r="E160" s="1"/>
+      <c r="F160" s="16"/>
       <c r="G160" s="1"/>
       <c r="H160" s="12"/>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A161" s="1" t="s">
-        <v>750</v>
+        <v>666</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>750</v>
+        <v>666</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>751</v>
+        <v>667</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>752</v>
-      </c>
-      <c r="E161" s="1" t="s">
-        <v>753</v>
-      </c>
-      <c r="F161" s="6" t="s">
-        <v>504</v>
-      </c>
+        <v>668</v>
+      </c>
+      <c r="E161" s="1"/>
+      <c r="F161" s="6"/>
       <c r="G161" s="1"/>
       <c r="H161" s="12"/>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A162" s="1" t="s">
-        <v>754</v>
+        <v>669</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>755</v>
+        <v>670</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>756</v>
+        <v>671</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>757</v>
+        <v>672</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>309</v>
+        <v>452</v>
       </c>
       <c r="F162" s="33" t="s">
-        <v>310</v>
-      </c>
-      <c r="G162" s="1"/>
-      <c r="H162" s="12"/>
+        <v>453</v>
+      </c>
+      <c r="G162" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H162" s="12">
+        <v>40000000</v>
+      </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A163" s="1" t="s">
-        <v>754</v>
+        <v>669</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>758</v>
+        <v>673</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>759</v>
+        <v>674</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>760</v>
+        <v>675</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>309</v>
+        <v>452</v>
       </c>
       <c r="F163" s="33" t="s">
-        <v>310</v>
-      </c>
-      <c r="G163" s="1"/>
-      <c r="H163" s="12"/>
+        <v>453</v>
+      </c>
+      <c r="G163" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H163" s="12">
+        <v>40000000</v>
+      </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A164" s="1" t="s">
-        <v>754</v>
+        <v>669</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>761</v>
+        <v>676</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>762</v>
+        <v>677</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>763</v>
+        <v>678</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>309</v>
+        <v>452</v>
       </c>
       <c r="F164" s="33" t="s">
-        <v>310</v>
-      </c>
-      <c r="G164" s="1"/>
-      <c r="H164" s="12"/>
+        <v>453</v>
+      </c>
+      <c r="G164" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H164" s="12">
+        <v>40000000</v>
+      </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A165" s="1" t="s">
-        <v>764</v>
+        <v>679</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>765</v>
+        <v>680</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>766</v>
+        <v>681</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>767</v>
+        <v>682</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>24</v>
+        <v>452</v>
       </c>
       <c r="F165" s="49" t="s">
-        <v>768</v>
-      </c>
-      <c r="G165" s="1"/>
-      <c r="H165" s="12"/>
+        <v>453</v>
+      </c>
+      <c r="G165" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H165" s="12">
+        <v>68000000</v>
+      </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A166" s="1" t="s">
-        <v>764</v>
+        <v>679</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>769</v>
+        <v>683</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>770</v>
+        <v>684</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>771</v>
+        <v>685</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>24</v>
+        <v>452</v>
       </c>
       <c r="F166" s="49" t="s">
-        <v>768</v>
-      </c>
-      <c r="G166" s="1"/>
-      <c r="H166" s="12"/>
+        <v>453</v>
+      </c>
+      <c r="G166" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H166" s="12">
+        <v>68000000</v>
+      </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A167" s="1" t="s">
-        <v>764</v>
+        <v>679</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>772</v>
+        <v>686</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>773</v>
+        <v>687</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>774</v>
+        <v>688</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>24</v>
+        <v>452</v>
       </c>
       <c r="F167" s="49" t="s">
-        <v>768</v>
-      </c>
-      <c r="G167" s="1"/>
-      <c r="H167" s="12"/>
+        <v>453</v>
+      </c>
+      <c r="G167" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H167" s="12">
+        <v>68000000</v>
+      </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A168" s="1" t="s">
-        <v>775</v>
+        <v>689</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>776</v>
+        <v>690</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>777</v>
+        <v>691</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>778</v>
-      </c>
-      <c r="E168" s="1" t="s">
-        <v>779</v>
-      </c>
-      <c r="F168" s="6" t="s">
-        <v>780</v>
-      </c>
+        <v>692</v>
+      </c>
+      <c r="E168" s="1"/>
+      <c r="F168" s="6"/>
       <c r="G168" s="1"/>
       <c r="H168" s="12"/>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A169" s="1" t="s">
-        <v>781</v>
+        <v>693</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>782</v>
+        <v>694</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>783</v>
+        <v>695</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>784</v>
-      </c>
-      <c r="E169" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="F169" s="37" t="s">
-        <v>500</v>
-      </c>
+        <v>696</v>
+      </c>
+      <c r="E169" s="1"/>
+      <c r="F169" s="37"/>
       <c r="G169" s="1"/>
       <c r="H169" s="12"/>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A170" s="1" t="s">
-        <v>781</v>
+        <v>693</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>785</v>
+        <v>697</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>786</v>
+        <v>698</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>787</v>
-      </c>
-      <c r="E170" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="F170" s="37" t="s">
-        <v>500</v>
-      </c>
+        <v>699</v>
+      </c>
+      <c r="E170" s="1"/>
+      <c r="F170" s="37"/>
       <c r="G170" s="1"/>
       <c r="H170" s="12"/>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A171" s="1" t="s">
-        <v>781</v>
+        <v>693</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>788</v>
+        <v>700</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>789</v>
+        <v>701</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>790</v>
-      </c>
-      <c r="E171" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="F171" s="37" t="s">
-        <v>500</v>
-      </c>
+        <v>702</v>
+      </c>
+      <c r="E171" s="1"/>
+      <c r="F171" s="37"/>
       <c r="G171" s="1"/>
       <c r="H171" s="12"/>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A172" s="1" t="s">
-        <v>781</v>
+        <v>693</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>791</v>
+        <v>703</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>792</v>
+        <v>704</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>793</v>
-      </c>
-      <c r="E172" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="F172" s="37" t="s">
-        <v>500</v>
-      </c>
+        <v>705</v>
+      </c>
+      <c r="E172" s="1"/>
+      <c r="F172" s="37"/>
       <c r="G172" s="1"/>
       <c r="H172" s="12"/>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A173" s="1" t="s">
-        <v>781</v>
+        <v>693</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>794</v>
+        <v>706</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>795</v>
+        <v>707</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>796</v>
-      </c>
-      <c r="E173" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="F173" s="37" t="s">
-        <v>500</v>
-      </c>
+        <v>708</v>
+      </c>
+      <c r="E173" s="1"/>
+      <c r="F173" s="37"/>
       <c r="G173" s="1"/>
       <c r="H173" s="12"/>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A174" s="1" t="s">
-        <v>797</v>
+        <v>709</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>798</v>
+        <v>710</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>799</v>
+        <v>711</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>800</v>
-      </c>
-      <c r="E174" s="1" t="s">
-        <v>466</v>
-      </c>
-      <c r="F174" s="6" t="s">
-        <v>467</v>
-      </c>
+        <v>712</v>
+      </c>
+      <c r="E174" s="1"/>
+      <c r="F174" s="6"/>
       <c r="G174" s="1"/>
       <c r="H174" s="12"/>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A175" s="1" t="s">
-        <v>797</v>
+        <v>709</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>801</v>
+        <v>713</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>802</v>
+        <v>714</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>803</v>
-      </c>
-      <c r="E175" s="1" t="s">
-        <v>466</v>
-      </c>
-      <c r="F175" s="6" t="s">
-        <v>467</v>
-      </c>
+        <v>715</v>
+      </c>
+      <c r="E175" s="1"/>
+      <c r="F175" s="6"/>
       <c r="G175" s="1"/>
       <c r="H175" s="12"/>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A176" s="1" t="s">
-        <v>797</v>
+        <v>709</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>804</v>
+        <v>716</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>805</v>
+        <v>717</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>806</v>
-      </c>
-      <c r="E176" s="1" t="s">
-        <v>466</v>
-      </c>
-      <c r="F176" s="6" t="s">
-        <v>467</v>
-      </c>
+        <v>718</v>
+      </c>
+      <c r="E176" s="1"/>
+      <c r="F176" s="6"/>
       <c r="G176" s="1"/>
       <c r="H176" s="12"/>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A177" s="1" t="s">
-        <v>797</v>
+        <v>709</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>807</v>
+        <v>719</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>808</v>
+        <v>720</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>809</v>
-      </c>
-      <c r="E177" s="1" t="s">
-        <v>466</v>
-      </c>
-      <c r="F177" s="6" t="s">
-        <v>467</v>
-      </c>
+        <v>721</v>
+      </c>
+      <c r="E177" s="1"/>
+      <c r="F177" s="6"/>
       <c r="G177" s="1"/>
       <c r="H177" s="12"/>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A178" s="1" t="s">
-        <v>810</v>
+        <v>722</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>811</v>
+        <v>723</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>812</v>
+        <v>724</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>813</v>
+        <v>725</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>814</v>
+        <v>71</v>
       </c>
       <c r="F178" s="50" t="s">
-        <v>815</v>
-      </c>
-      <c r="G178" s="1"/>
-      <c r="H178" s="12"/>
+        <v>83</v>
+      </c>
+      <c r="G178" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H178" s="12">
+        <v>33000000</v>
+      </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A179" s="1" t="s">
-        <v>816</v>
+        <v>726</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>817</v>
+        <v>727</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>818</v>
+        <v>728</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>819</v>
+        <v>729</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>814</v>
+        <v>886</v>
       </c>
       <c r="F179" s="50" t="s">
-        <v>815</v>
-      </c>
-      <c r="G179" s="1"/>
-      <c r="H179" s="12"/>
+        <v>887</v>
+      </c>
+      <c r="G179" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H179" s="12">
+        <v>1450000000</v>
+      </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A180" s="1" t="s">
-        <v>816</v>
+        <v>726</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>820</v>
+        <v>730</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>821</v>
+        <v>731</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>822</v>
+        <v>732</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>814</v>
+        <v>886</v>
       </c>
       <c r="F180" s="50" t="s">
-        <v>815</v>
-      </c>
-      <c r="G180" s="1"/>
-      <c r="H180" s="12"/>
+        <v>887</v>
+      </c>
+      <c r="G180" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H180" s="12">
+        <v>1450000000</v>
+      </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A181" s="1" t="s">
-        <v>823</v>
+        <v>733</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>824</v>
+        <v>734</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>825</v>
+        <v>735</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>826</v>
+        <v>736</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>827</v>
+        <v>118</v>
       </c>
       <c r="F181" s="51" t="s">
-        <v>828</v>
-      </c>
-      <c r="G181" s="1"/>
-      <c r="H181" s="12"/>
+        <v>119</v>
+      </c>
+      <c r="G181" s="1" t="s">
+        <v>877</v>
+      </c>
+      <c r="H181" s="12">
+        <v>45000000</v>
+      </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A182" s="1" t="s">
-        <v>829</v>
+        <v>739</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>829</v>
+        <v>739</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>830</v>
+        <v>740</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>831</v>
+        <v>741</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>832</v>
+        <v>888</v>
       </c>
       <c r="F182" s="52" t="s">
-        <v>833</v>
-      </c>
-      <c r="G182" s="1"/>
-      <c r="H182" s="12"/>
+        <v>889</v>
+      </c>
+      <c r="G182" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H182" s="12">
+        <v>52000000</v>
+      </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A183" s="1" t="s">
-        <v>834</v>
+        <v>743</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>835</v>
+        <v>744</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>836</v>
+        <v>745</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>837</v>
+        <v>746</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>52</v>
+        <v>169</v>
       </c>
       <c r="F183" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G183" s="1"/>
-      <c r="H183" s="12"/>
+        <v>512</v>
+      </c>
+      <c r="G183" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H183" s="12">
+        <v>80000000</v>
+      </c>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A184" s="1" t="s">
-        <v>838</v>
+        <v>747</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>839</v>
+        <v>748</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>840</v>
+        <v>749</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>841</v>
+        <v>750</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>24</v>
+        <v>461</v>
       </c>
       <c r="F184" s="49" t="s">
-        <v>768</v>
-      </c>
-      <c r="G184" s="1"/>
-      <c r="H184" s="12"/>
+        <v>462</v>
+      </c>
+      <c r="G184" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H184" s="12">
+        <v>66000000</v>
+      </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A185" s="1" t="s">
-        <v>842</v>
+        <v>751</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>842</v>
+        <v>751</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>843</v>
+        <v>752</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>844</v>
+        <v>753</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>123</v>
+        <v>461</v>
       </c>
       <c r="F185" s="20" t="s">
-        <v>124</v>
-      </c>
-      <c r="G185" s="1"/>
-      <c r="H185" s="12"/>
+        <v>890</v>
+      </c>
+      <c r="G185" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H185" s="12">
+        <v>78000000</v>
+      </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A186" s="1" t="s">
-        <v>845</v>
+        <v>754</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>846</v>
+        <v>755</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>847</v>
+        <v>756</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>848</v>
+        <v>757</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>24</v>
+        <v>461</v>
       </c>
       <c r="F186" s="49" t="s">
-        <v>768</v>
-      </c>
-      <c r="G186" s="1"/>
-      <c r="H186" s="12"/>
+        <v>890</v>
+      </c>
+      <c r="G186" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H186" s="12">
+        <v>35000000</v>
+      </c>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A187" s="1" t="s">
-        <v>849</v>
+        <v>758</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>849</v>
+        <v>758</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>850</v>
+        <v>759</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>851</v>
+        <v>760</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>169</v>
+        <v>543</v>
       </c>
       <c r="F187" s="13" t="s">
-        <v>571</v>
-      </c>
-      <c r="G187" s="1"/>
-      <c r="H187" s="12"/>
+        <v>869</v>
+      </c>
+      <c r="G187" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H187" s="12">
+        <v>25000000</v>
+      </c>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A188" s="1" t="s">
-        <v>852</v>
+        <v>761</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>853</v>
+        <v>762</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>854</v>
+        <v>763</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>855</v>
+        <v>764</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>692</v>
+        <v>527</v>
       </c>
       <c r="F188" s="47" t="s">
-        <v>693</v>
-      </c>
-      <c r="G188" s="1"/>
-      <c r="H188" s="12"/>
+        <v>528</v>
+      </c>
+      <c r="G188" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H188" s="12">
+        <v>66000000</v>
+      </c>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A189" s="1" t="s">
-        <v>856</v>
+        <v>765</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>857</v>
+        <v>766</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>858</v>
+        <v>767</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>859</v>
+        <v>768</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>590</v>
+        <v>123</v>
       </c>
       <c r="F189" s="41" t="s">
-        <v>591</v>
-      </c>
-      <c r="G189" s="1"/>
-      <c r="H189" s="12"/>
+        <v>124</v>
+      </c>
+      <c r="G189" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H189" s="12">
+        <v>115000000</v>
+      </c>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A190" s="1" t="s">
-        <v>860</v>
+        <v>769</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>861</v>
+        <v>770</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>862</v>
+        <v>771</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>863</v>
+        <v>772</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>864</v>
+        <v>95</v>
       </c>
       <c r="F190" s="53" t="s">
-        <v>865</v>
-      </c>
-      <c r="G190" s="1"/>
-      <c r="H190" s="12"/>
+        <v>96</v>
+      </c>
+      <c r="G190" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H190" s="12">
+        <v>80000000</v>
+      </c>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A191" s="1" t="s">
-        <v>866</v>
+        <v>773</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>866</v>
+        <v>773</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>867</v>
+        <v>774</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>868</v>
+        <v>775</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="F191" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="G191" s="1"/>
-      <c r="H191" s="12"/>
+        <v>46</v>
+      </c>
+      <c r="G191" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H191" s="12">
+        <v>33000000</v>
+      </c>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A192" s="1" t="s">
-        <v>869</v>
+        <v>776</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>870</v>
+        <v>777</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>871</v>
+        <v>778</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>872</v>
-      </c>
-      <c r="E192" s="1" t="s">
-        <v>832</v>
-      </c>
-      <c r="F192" s="52" t="s">
-        <v>833</v>
-      </c>
+        <v>779</v>
+      </c>
+      <c r="E192" s="1"/>
+      <c r="F192" s="52"/>
       <c r="G192" s="1"/>
       <c r="H192" s="12"/>
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A193" s="1" t="s">
-        <v>869</v>
+        <v>776</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>873</v>
+        <v>780</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>874</v>
+        <v>781</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>875</v>
-      </c>
-      <c r="E193" s="1" t="s">
-        <v>832</v>
-      </c>
-      <c r="F193" s="52" t="s">
-        <v>833</v>
-      </c>
+        <v>782</v>
+      </c>
+      <c r="E193" s="1"/>
+      <c r="F193" s="52"/>
       <c r="G193" s="1"/>
       <c r="H193" s="12"/>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A194" s="1" t="s">
-        <v>876</v>
+        <v>783</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>876</v>
+        <v>783</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>877</v>
+        <v>784</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>878</v>
+        <v>785</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>652</v>
+        <v>12</v>
       </c>
       <c r="F194" s="44" t="s">
-        <v>653</v>
-      </c>
-      <c r="G194" s="1"/>
-      <c r="H194" s="12"/>
+        <v>885</v>
+      </c>
+      <c r="G194" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H194" s="12">
+        <v>175000000</v>
+      </c>
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A195" s="1" t="s">
-        <v>876</v>
+        <v>783</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>879</v>
+        <v>786</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>880</v>
+        <v>787</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>881</v>
+        <v>788</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>652</v>
+        <v>12</v>
       </c>
       <c r="F195" s="44" t="s">
-        <v>653</v>
-      </c>
-      <c r="G195" s="1"/>
-      <c r="H195" s="12"/>
+        <v>885</v>
+      </c>
+      <c r="G195" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H195" s="12">
+        <v>175000000</v>
+      </c>
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A196" s="1" t="s">
-        <v>882</v>
+        <v>789</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>882</v>
+        <v>789</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>883</v>
+        <v>790</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>884</v>
+        <v>791</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>70</v>
+        <v>881</v>
       </c>
       <c r="F196" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="G196" s="1"/>
-      <c r="H196" s="12"/>
+        <v>198</v>
+      </c>
+      <c r="G196" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H196" s="12">
+        <v>44500000</v>
+      </c>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A197" s="1" t="s">
-        <v>885</v>
+        <v>792</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>886</v>
+        <v>793</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>887</v>
+        <v>794</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>888</v>
-      </c>
-      <c r="E197" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F197" s="6" t="s">
-        <v>12</v>
-      </c>
+        <v>795</v>
+      </c>
+      <c r="E197" s="1"/>
+      <c r="F197" s="6"/>
       <c r="G197" s="1"/>
       <c r="H197" s="12"/>
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A198" s="1" t="s">
-        <v>889</v>
+        <v>796</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>890</v>
+        <v>797</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>891</v>
+        <v>798</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>892</v>
-      </c>
-      <c r="E198" s="1" t="s">
-        <v>893</v>
-      </c>
-      <c r="F198" s="6" t="s">
-        <v>894</v>
-      </c>
+        <v>799</v>
+      </c>
+      <c r="E198" s="1"/>
+      <c r="F198" s="6"/>
       <c r="G198" s="1"/>
       <c r="H198" s="12"/>
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A199" s="1" t="s">
-        <v>895</v>
+        <v>800</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>896</v>
+        <v>801</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>897</v>
+        <v>802</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>898</v>
+        <v>803</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>899</v>
+        <v>289</v>
       </c>
       <c r="F199" s="6" t="s">
-        <v>900</v>
-      </c>
-      <c r="G199" s="1"/>
-      <c r="H199" s="12"/>
+        <v>873</v>
+      </c>
+      <c r="G199" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H199" s="12">
+        <v>30000000</v>
+      </c>
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A200" s="1" t="s">
-        <v>895</v>
+        <v>800</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>901</v>
+        <v>804</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>902</v>
+        <v>805</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>903</v>
+        <v>806</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>899</v>
+        <v>289</v>
       </c>
       <c r="F200" s="6" t="s">
-        <v>900</v>
-      </c>
-      <c r="G200" s="1"/>
-      <c r="H200" s="12"/>
+        <v>873</v>
+      </c>
+      <c r="G200" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H200" s="12">
+        <v>30000000</v>
+      </c>
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A201" s="1" t="s">
-        <v>904</v>
+        <v>807</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>905</v>
+        <v>808</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>906</v>
+        <v>809</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>907</v>
-      </c>
-      <c r="E201" s="1" t="s">
-        <v>908</v>
-      </c>
-      <c r="F201" s="6" t="s">
-        <v>909</v>
-      </c>
+        <v>810</v>
+      </c>
+      <c r="E201" s="1"/>
+      <c r="F201" s="6"/>
       <c r="G201" s="1"/>
       <c r="H201" s="12"/>
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A202" s="1" t="s">
-        <v>910</v>
+        <v>811</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>910</v>
+        <v>811</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>911</v>
+        <v>812</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>912</v>
-      </c>
-      <c r="E202" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="F202" s="6" t="s">
-        <v>913</v>
-      </c>
+        <v>813</v>
+      </c>
+      <c r="E202" s="1"/>
+      <c r="F202" s="6"/>
       <c r="G202" s="1"/>
       <c r="H202" s="12"/>
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A203" s="1" t="s">
-        <v>914</v>
+        <v>814</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>914</v>
+        <v>814</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>915</v>
+        <v>815</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>916</v>
-      </c>
-      <c r="E203" s="1" t="s">
-        <v>917</v>
-      </c>
-      <c r="F203" s="6" t="s">
-        <v>918</v>
-      </c>
+        <v>816</v>
+      </c>
+      <c r="E203" s="1"/>
+      <c r="F203" s="6"/>
       <c r="G203" s="1"/>
       <c r="H203" s="12"/>
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A204" s="1" t="s">
-        <v>919</v>
+        <v>817</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>919</v>
+        <v>817</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>920</v>
+        <v>818</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>921</v>
+        <v>819</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>922</v>
+        <v>737</v>
       </c>
       <c r="F204" s="6" t="s">
-        <v>923</v>
-      </c>
-      <c r="G204" s="1"/>
-      <c r="H204" s="12"/>
+        <v>738</v>
+      </c>
+      <c r="G204" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H204" s="12">
+        <v>110000000</v>
+      </c>
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A205" s="1" t="s">
-        <v>924</v>
+        <v>820</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>924</v>
+        <v>820</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>925</v>
+        <v>821</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>926</v>
-      </c>
-      <c r="E205" s="1" t="s">
-        <v>927</v>
-      </c>
-      <c r="F205" s="6" t="s">
-        <v>928</v>
-      </c>
+        <v>822</v>
+      </c>
+      <c r="E205" s="1"/>
+      <c r="F205" s="6"/>
       <c r="G205" s="1"/>
       <c r="H205" s="12"/>
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A206" s="1" t="s">
-        <v>929</v>
+        <v>823</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>930</v>
+        <v>824</v>
       </c>
       <c r="C206" s="1" t="s">
-        <v>931</v>
+        <v>825</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>932</v>
+        <v>826</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>927</v>
+        <v>891</v>
       </c>
       <c r="F206" s="6" t="s">
-        <v>928</v>
-      </c>
-      <c r="G206" s="1"/>
-      <c r="H206" s="12"/>
+        <v>892</v>
+      </c>
+      <c r="G206" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H206" s="12">
+        <v>28400000</v>
+      </c>
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A207" s="1" t="s">
-        <v>933</v>
+        <v>827</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>934</v>
+        <v>828</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>935</v>
+        <v>829</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>936</v>
-      </c>
-      <c r="E207" s="1" t="s">
-        <v>937</v>
-      </c>
-      <c r="F207" s="6" t="s">
-        <v>938</v>
-      </c>
+        <v>830</v>
+      </c>
+      <c r="E207" s="1"/>
+      <c r="F207" s="6"/>
       <c r="G207" s="1"/>
       <c r="H207" s="12"/>
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A208" s="1" t="s">
-        <v>933</v>
+        <v>827</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>939</v>
+        <v>831</v>
       </c>
       <c r="C208" s="1" t="s">
-        <v>940</v>
+        <v>832</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>941</v>
-      </c>
-      <c r="E208" s="1" t="s">
-        <v>937</v>
-      </c>
-      <c r="F208" s="6" t="s">
-        <v>938</v>
-      </c>
+        <v>833</v>
+      </c>
+      <c r="E208" s="1"/>
+      <c r="F208" s="6"/>
       <c r="G208" s="1"/>
       <c r="H208" s="12"/>
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A209" s="1" t="s">
-        <v>933</v>
+        <v>827</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>942</v>
+        <v>834</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>943</v>
+        <v>835</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>944</v>
-      </c>
-      <c r="E209" s="1" t="s">
-        <v>937</v>
-      </c>
-      <c r="F209" s="6" t="s">
-        <v>938</v>
-      </c>
+        <v>836</v>
+      </c>
+      <c r="E209" s="1"/>
+      <c r="F209" s="6"/>
       <c r="G209" s="1"/>
       <c r="H209" s="12"/>
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A210" s="1" t="s">
-        <v>945</v>
+        <v>837</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>945</v>
+        <v>837</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>946</v>
+        <v>838</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>947</v>
+        <v>839</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>948</v>
+        <v>261</v>
       </c>
       <c r="F210" s="6" t="s">
-        <v>949</v>
-      </c>
-      <c r="G210" s="1"/>
-      <c r="H210" s="12"/>
+        <v>262</v>
+      </c>
+      <c r="G210" s="1" t="s">
+        <v>877</v>
+      </c>
+      <c r="H210" s="12">
+        <v>46200000</v>
+      </c>
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A211" s="1" t="s">
-        <v>950</v>
+        <v>840</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>951</v>
+        <v>841</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>952</v>
+        <v>842</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>953</v>
+        <v>843</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>954</v>
+        <v>129</v>
       </c>
       <c r="F211" s="6" t="s">
-        <v>955</v>
-      </c>
-      <c r="G211" s="1"/>
-      <c r="H211" s="12"/>
+        <v>130</v>
+      </c>
+      <c r="G211" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H211" s="12">
+        <v>50000000</v>
+      </c>
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A212" s="1" t="s">
-        <v>956</v>
+        <v>844</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>956</v>
+        <v>844</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>957</v>
+        <v>845</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>958</v>
+        <v>846</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>959</v>
+        <v>174</v>
       </c>
       <c r="F212" s="6" t="s">
-        <v>960</v>
-      </c>
-      <c r="G212" s="1"/>
-      <c r="H212" s="12"/>
+        <v>175</v>
+      </c>
+      <c r="G212" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H212" s="12">
+        <v>39600000</v>
+      </c>
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A213" s="1" t="s">
-        <v>961</v>
+        <v>847</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>962</v>
+        <v>848</v>
       </c>
       <c r="C213" s="1" t="s">
-        <v>963</v>
+        <v>849</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>964</v>
+        <v>850</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>937</v>
+        <v>527</v>
       </c>
       <c r="F213" s="6" t="s">
-        <v>938</v>
-      </c>
-      <c r="G213" s="1"/>
-      <c r="H213" s="12"/>
+        <v>528</v>
+      </c>
+      <c r="G213" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H213" s="12">
+        <v>42000000</v>
+      </c>
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A214" s="1" t="s">
-        <v>965</v>
+        <v>851</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>965</v>
+        <v>851</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>966</v>
+        <v>852</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>967</v>
-      </c>
-      <c r="E214" s="1" t="s">
-        <v>968</v>
-      </c>
-      <c r="F214" s="6" t="s">
-        <v>969</v>
-      </c>
+        <v>853</v>
+      </c>
+      <c r="E214" s="1"/>
+      <c r="F214" s="6"/>
       <c r="G214" s="1"/>
       <c r="H214" s="12"/>
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A215" s="1" t="s">
-        <v>970</v>
+        <v>854</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>971</v>
+        <v>855</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>972</v>
+        <v>856</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>973</v>
-      </c>
-      <c r="E215" s="1" t="s">
-        <v>974</v>
-      </c>
-      <c r="F215" s="6" t="s">
-        <v>975</v>
-      </c>
+        <v>857</v>
+      </c>
+      <c r="E215" s="1"/>
+      <c r="F215" s="6"/>
       <c r="G215" s="1"/>
       <c r="H215" s="12"/>
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A216" s="1" t="s">
-        <v>976</v>
+        <v>858</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>977</v>
+        <v>859</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>978</v>
+        <v>860</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>979</v>
-      </c>
-      <c r="E216" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F216" s="6" t="s">
-        <v>154</v>
-      </c>
+        <v>861</v>
+      </c>
+      <c r="E216" s="1"/>
+      <c r="F216" s="6"/>
       <c r="G216" s="1"/>
       <c r="H216" s="12"/>
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A217" s="1" t="s">
-        <v>980</v>
+        <v>862</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>980</v>
+        <v>862</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>981</v>
+        <v>863</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>982</v>
-      </c>
-      <c r="E217" s="1" t="s">
-        <v>832</v>
-      </c>
-      <c r="F217" s="52" t="s">
-        <v>833</v>
-      </c>
+        <v>864</v>
+      </c>
+      <c r="E217" s="1"/>
+      <c r="F217" s="52"/>
       <c r="G217" s="1"/>
       <c r="H217" s="12"/>
     </row>
@@ -9819,6 +8639,7 @@
       <c r="F230"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H217" xr:uid="{227F6D87-73E7-4864-B070-B701701C2209}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Campaigns_Master.xlsx
+++ b/Campaigns_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Good KoDz\Banner Monitor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2EEE659-7131-47F5-8F73-3D86EB815B3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE293E8F-61DA-49E3-A452-B2531F73C3C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EBB7D5F9-BF11-4273-8F7B-7CCC7D024DDF}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1321" uniqueCount="893">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1321" uniqueCount="892">
   <si>
     <t>Campaign Name</t>
   </si>
@@ -2670,9 +2670,6 @@
   </si>
   <si>
     <t>1405/08/25</t>
-  </si>
-  <si>
-    <t>shahrzad</t>
   </si>
   <si>
     <t>1405/06/25</t>
@@ -3493,7 +3490,7 @@
     <col min="5" max="5" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.33203125" style="54" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
@@ -5417,7 +5414,7 @@
         <v>876</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>877</v>
+        <v>13</v>
       </c>
       <c r="H77" s="12">
         <v>46200000</v>
@@ -5495,7 +5492,7 @@
         <v>89</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>877</v>
+        <v>13</v>
       </c>
       <c r="H80" s="12">
         <v>41580000</v>
@@ -5521,7 +5518,7 @@
         <v>130</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>877</v>
+        <v>13</v>
       </c>
       <c r="H81" s="12">
         <v>6600000</v>
@@ -5547,7 +5544,7 @@
         <v>93</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>877</v>
+        <v>13</v>
       </c>
       <c r="H82" s="12">
         <v>49500000</v>
@@ -5570,7 +5567,7 @@
         <v>432</v>
       </c>
       <c r="F83" s="6" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="G83" s="1" t="s">
         <v>865</v>
@@ -5651,7 +5648,7 @@
         <v>873</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>877</v>
+        <v>13</v>
       </c>
       <c r="H86" s="12">
         <v>30000000</v>
@@ -5829,10 +5826,10 @@
         <v>422</v>
       </c>
       <c r="E94" s="1" t="s">
+        <v>878</v>
+      </c>
+      <c r="F94" s="36" t="s">
         <v>879</v>
-      </c>
-      <c r="F94" s="36" t="s">
-        <v>880</v>
       </c>
       <c r="G94" s="1" t="s">
         <v>865</v>
@@ -6029,7 +6026,7 @@
         <v>457</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>198</v>
@@ -6549,7 +6546,7 @@
         <v>542</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>872</v>
@@ -6599,7 +6596,7 @@
         <v>53</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>877</v>
+        <v>13</v>
       </c>
       <c r="H128" s="12">
         <v>58000000</v>
@@ -6637,13 +6634,13 @@
         <v>557</v>
       </c>
       <c r="E130" s="1" t="s">
+        <v>882</v>
+      </c>
+      <c r="F130" s="6" t="s">
         <v>883</v>
       </c>
-      <c r="F130" s="6" t="s">
-        <v>884</v>
-      </c>
       <c r="G130" s="1" t="s">
-        <v>877</v>
+        <v>13</v>
       </c>
       <c r="H130" s="12">
         <v>82500000</v>
@@ -6663,13 +6660,13 @@
         <v>560</v>
       </c>
       <c r="E131" s="1" t="s">
+        <v>882</v>
+      </c>
+      <c r="F131" s="6" t="s">
         <v>883</v>
       </c>
-      <c r="F131" s="6" t="s">
-        <v>884</v>
-      </c>
       <c r="G131" s="1" t="s">
-        <v>877</v>
+        <v>13</v>
       </c>
       <c r="H131" s="12">
         <v>82500000</v>
@@ -6689,13 +6686,13 @@
         <v>563</v>
       </c>
       <c r="E132" s="1" t="s">
+        <v>882</v>
+      </c>
+      <c r="F132" s="6" t="s">
         <v>883</v>
       </c>
-      <c r="F132" s="6" t="s">
-        <v>884</v>
-      </c>
       <c r="G132" s="1" t="s">
-        <v>877</v>
+        <v>13</v>
       </c>
       <c r="H132" s="12">
         <v>82500000</v>
@@ -6736,7 +6733,7 @@
         <v>12</v>
       </c>
       <c r="F134" s="13" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="G134" s="1" t="s">
         <v>20</v>
@@ -7102,7 +7099,7 @@
         <v>41</v>
       </c>
       <c r="H150" s="12">
-        <v>330000000</v>
+        <v>33000000</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.3">
@@ -7140,7 +7137,7 @@
         <v>12</v>
       </c>
       <c r="F152" s="6" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="G152" s="1" t="s">
         <v>61</v>
@@ -7166,7 +7163,7 @@
         <v>12</v>
       </c>
       <c r="F153" s="6" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="G153" s="1" t="s">
         <v>61</v>
@@ -7192,7 +7189,7 @@
         <v>12</v>
       </c>
       <c r="F154" s="6" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="G154" s="1" t="s">
         <v>61</v>
@@ -7218,7 +7215,7 @@
         <v>12</v>
       </c>
       <c r="F155" s="6" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="G155" s="1" t="s">
         <v>61</v>
@@ -7244,7 +7241,7 @@
         <v>12</v>
       </c>
       <c r="F156" s="6" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="G156" s="1" t="s">
         <v>61</v>
@@ -7719,16 +7716,16 @@
         <v>729</v>
       </c>
       <c r="E179" s="1" t="s">
+        <v>885</v>
+      </c>
+      <c r="F179" s="50" t="s">
         <v>886</v>
-      </c>
-      <c r="F179" s="50" t="s">
-        <v>887</v>
       </c>
       <c r="G179" s="1" t="s">
         <v>61</v>
       </c>
       <c r="H179" s="12">
-        <v>1450000000</v>
+        <v>145000000</v>
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.3">
@@ -7745,16 +7742,16 @@
         <v>732</v>
       </c>
       <c r="E180" s="1" t="s">
+        <v>885</v>
+      </c>
+      <c r="F180" s="50" t="s">
         <v>886</v>
-      </c>
-      <c r="F180" s="50" t="s">
-        <v>887</v>
       </c>
       <c r="G180" s="1" t="s">
         <v>61</v>
       </c>
       <c r="H180" s="12">
-        <v>1450000000</v>
+        <v>145000000</v>
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.3">
@@ -7777,7 +7774,7 @@
         <v>119</v>
       </c>
       <c r="G181" s="1" t="s">
-        <v>877</v>
+        <v>13</v>
       </c>
       <c r="H181" s="12">
         <v>45000000</v>
@@ -7797,10 +7794,10 @@
         <v>741</v>
       </c>
       <c r="E182" s="1" t="s">
+        <v>887</v>
+      </c>
+      <c r="F182" s="52" t="s">
         <v>888</v>
-      </c>
-      <c r="F182" s="52" t="s">
-        <v>889</v>
       </c>
       <c r="G182" s="1" t="s">
         <v>47</v>
@@ -7878,7 +7875,7 @@
         <v>461</v>
       </c>
       <c r="F185" s="20" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="G185" s="1" t="s">
         <v>47</v>
@@ -7904,7 +7901,7 @@
         <v>461</v>
       </c>
       <c r="F186" s="49" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="G186" s="1" t="s">
         <v>61</v>
@@ -8096,7 +8093,7 @@
         <v>12</v>
       </c>
       <c r="F194" s="44" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="G194" s="1" t="s">
         <v>61</v>
@@ -8122,7 +8119,7 @@
         <v>12</v>
       </c>
       <c r="F195" s="44" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="G195" s="1" t="s">
         <v>61</v>
@@ -8145,7 +8142,7 @@
         <v>791</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="F196" s="6" t="s">
         <v>198</v>
@@ -8357,10 +8354,10 @@
         <v>826</v>
       </c>
       <c r="E206" s="1" t="s">
+        <v>890</v>
+      </c>
+      <c r="F206" s="6" t="s">
         <v>891</v>
-      </c>
-      <c r="F206" s="6" t="s">
-        <v>892</v>
       </c>
       <c r="G206" s="1" t="s">
         <v>61</v>
@@ -8443,7 +8440,7 @@
         <v>262</v>
       </c>
       <c r="G210" s="1" t="s">
-        <v>877</v>
+        <v>13</v>
       </c>
       <c r="H210" s="12">
         <v>46200000</v>
